--- a/travel/보홀/2026_보홀.xlsx
+++ b/travel/보홀/2026_보홀.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\보홀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E81DFA9B-030E-415A-9CC5-142ED06C5BA2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8CAE8C-F01A-4B5A-BC09-FFC42F907FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
   <si>
     <t>토</t>
   </si>
@@ -354,7 +354,31 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>리조트캉스</t>
+    <t>아고타타</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비그랜드 리조트</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팡라오 체크인 (14:00)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>팡라오 체크아웃 (12:00)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비그랜드 체크인 (15:00)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>비그랜드 체크아웃 (12:00)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>숙소(비그랜드리조트)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -451,7 +475,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -506,8 +530,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="18">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -656,19 +686,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -756,7 +773,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -790,33 +807,6 @@
     <xf numFmtId="20" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -827,9 +817,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
@@ -856,29 +843,65 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="20" fontId="0" fillId="2" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="15" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1069,6 +1092,50 @@
         <a:xfrm>
           <a:off x="14820900" y="209549"/>
           <a:ext cx="5848350" cy="5156295"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>156842</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D81A491A-47D1-1479-13F5-A8E1FE6E8F34}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="733425" y="5676900"/>
+          <a:ext cx="7505700" cy="6424292"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1405,10 +1472,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="45.75">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="19" t="s">
         <v>40</v>
       </c>
     </row>
@@ -1486,11 +1553,11 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="20">
+      <c r="K4" s="11">
         <v>0.50694444444444442</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" ht="17.25" thickBot="1">
       <c r="B5" s="9">
         <v>4.1666666666666664E-2</v>
       </c>
@@ -1502,7 +1569,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="21" t="s">
+      <c r="K5" s="14" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1511,7 +1578,7 @@
         <v>8.3333333333333301E-2</v>
       </c>
       <c r="C6" s="6"/>
-      <c r="D6" s="24">
+      <c r="D6" s="11">
         <v>9.375E-2</v>
       </c>
       <c r="E6" s="3"/>
@@ -1520,13 +1587,14 @@
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="1:13" ht="17.25" thickBot="1">
       <c r="B7" s="9">
         <v>0.125</v>
       </c>
       <c r="C7" s="6"/>
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="14" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="3"/>
@@ -1535,12 +1603,14 @@
       <c r="H7" s="3"/>
       <c r="I7" s="3"/>
       <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="K7" s="5"/>
+    </row>
+    <row r="8" spans="1:13" ht="17.25" thickBot="1">
       <c r="B8" s="9">
         <v>0.16666666666666699</v>
       </c>
       <c r="C8" s="6"/>
+      <c r="D8" s="5"/>
       <c r="E8" s="3"/>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
@@ -1554,7 +1624,7 @@
         <v>0.20833333333333301</v>
       </c>
       <c r="C9" s="6"/>
-      <c r="D9" s="22">
+      <c r="D9" s="11">
         <v>0.2361111111111111</v>
       </c>
       <c r="E9" s="3"/>
@@ -1563,7 +1633,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="22">
+      <c r="K9" s="11">
         <v>0.22222222222222221</v>
       </c>
     </row>
@@ -1572,7 +1642,7 @@
         <v>0.25</v>
       </c>
       <c r="C10" s="6"/>
-      <c r="D10" s="23" t="s">
+      <c r="D10" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="3"/>
@@ -1581,7 +1651,7 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="3"/>
-      <c r="K10" s="23" t="s">
+      <c r="K10" s="14" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1618,7 +1688,7 @@
         <v>0.375</v>
       </c>
       <c r="C13" s="6"/>
-      <c r="D13" s="20">
+      <c r="D13" s="11">
         <v>0.39930555555555558</v>
       </c>
       <c r="E13" s="3"/>
@@ -1634,7 +1704,7 @@
         <v>0.41666666666666702</v>
       </c>
       <c r="C14" s="6"/>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="12" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="3"/>
@@ -1650,7 +1720,7 @@
         <v>0.45833333333333298</v>
       </c>
       <c r="C15" s="6"/>
-      <c r="D15" s="22">
+      <c r="D15" s="13">
         <v>0.47222222222222221</v>
       </c>
       <c r="E15" s="3"/>
@@ -1666,15 +1736,19 @@
         <v>0.5</v>
       </c>
       <c r="C16" s="6"/>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="14" t="s">
         <v>16</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="H16" s="3" t="s">
+        <v>72</v>
+      </c>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
+      <c r="J16" s="3" t="s">
+        <v>74</v>
+      </c>
       <c r="K16" s="5"/>
     </row>
     <row r="17" spans="2:11">
@@ -1696,7 +1770,9 @@
         <v>0.58333333333333304</v>
       </c>
       <c r="C18" s="6"/>
-      <c r="D18" s="3"/>
+      <c r="D18" s="3" t="s">
+        <v>71</v>
+      </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
@@ -1714,7 +1790,9 @@
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
+      <c r="H19" s="3" t="s">
+        <v>73</v>
+      </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="5"/>
@@ -1787,7 +1865,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="J24" s="20">
+      <c r="J24" s="11">
         <v>0.85069444444444442</v>
       </c>
       <c r="K24" s="5"/>
@@ -1803,7 +1881,7 @@
       <c r="G25" s="3"/>
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
-      <c r="J25" s="21" t="s">
+      <c r="J25" s="12" t="s">
         <v>16</v>
       </c>
       <c r="K25" s="5"/>
@@ -1819,7 +1897,7 @@
       <c r="G26" s="3"/>
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
-      <c r="J26" s="22">
+      <c r="J26" s="13">
         <v>0.92013888888888884</v>
       </c>
       <c r="K26" s="5"/>
@@ -1837,7 +1915,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="35" t="s">
+      <c r="J27" s="25" t="s">
         <v>17</v>
       </c>
       <c r="K27" s="5"/>
@@ -1846,19 +1924,19 @@
       <c r="B28" s="10">
         <v>1</v>
       </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="39" t="s">
+      <c r="C28" s="23"/>
+      <c r="D28" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="E28" s="37"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="37"/>
-      <c r="H28" s="40"/>
-      <c r="I28" s="37" t="s">
-        <v>69</v>
-      </c>
-      <c r="J28" s="38"/>
-      <c r="K28" s="34"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="J28" s="33"/>
+      <c r="K28" s="24"/>
     </row>
     <row r="31" spans="2:11">
       <c r="C31" t="s">
@@ -1898,6 +1976,9 @@
       </c>
     </row>
     <row r="36" spans="3:9">
+      <c r="C36" t="s">
+        <v>69</v>
+      </c>
       <c r="E36" t="s">
         <v>24</v>
       </c>
@@ -1924,27 +2005,27 @@
       </c>
     </row>
     <row r="46" spans="3:9" ht="36">
-      <c r="D46" s="26" t="s">
+      <c r="D46" s="16" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="47" spans="3:9" ht="36">
-      <c r="D47" s="27" t="s">
+      <c r="D47" s="17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="48" spans="3:9" ht="36">
-      <c r="D48" s="26" t="s">
+      <c r="D48" s="16" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="49" spans="4:4" ht="54">
-      <c r="D49" s="26" t="s">
+      <c r="D49" s="16" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="50" spans="4:4" ht="33.75">
-      <c r="D50" s="28" t="s">
+      <c r="D50" s="18" t="s">
         <v>39</v>
       </c>
     </row>
@@ -1964,170 +2045,175 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
-    <col min="2" max="2" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="B2" s="11"/>
-      <c r="C2" s="36" t="s">
+      <c r="B2" s="26"/>
+      <c r="C2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="36" t="s">
+      <c r="E2" s="26" t="s">
         <v>12</v>
       </c>
+      <c r="F2" s="34"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="36">
         <v>985619</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="14"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" spans="2:6">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="13">
+      <c r="C4" s="36">
         <v>345632</v>
       </c>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="14"/>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="37"/>
     </row>
     <row r="5" spans="2:6">
-      <c r="B5" s="12"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="14"/>
+      <c r="B5" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="36">
+        <v>348623</v>
+      </c>
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="37"/>
     </row>
     <row r="6" spans="2:6">
-      <c r="B6" s="12"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="14"/>
+      <c r="B6" s="35"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="37"/>
     </row>
     <row r="7" spans="2:6">
-      <c r="B7" s="12"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="14"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="37"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="12"/>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="14"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="37"/>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="12"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="14"/>
+      <c r="B9" s="35"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="37"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="12"/>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="14"/>
+      <c r="B10" s="35"/>
+      <c r="C10" s="36"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="37"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="12"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="14"/>
+      <c r="B11" s="35"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="37"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="12"/>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="14"/>
+      <c r="B12" s="35"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="37"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="12"/>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="14"/>
+      <c r="B13" s="35"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="37"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="12"/>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="13"/>
-      <c r="F14" s="14"/>
+      <c r="B14" s="35"/>
+      <c r="C14" s="36"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="37"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="12"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="14"/>
+      <c r="B15" s="35"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="37"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="14"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="36"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="37"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="12"/>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="14"/>
+      <c r="B17" s="35"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="36"/>
+      <c r="F17" s="37"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="14"/>
+      <c r="B18" s="35"/>
+      <c r="C18" s="36"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="36"/>
+      <c r="F18" s="37"/>
     </row>
     <row r="19" spans="2:6" ht="17.25" thickBot="1">
-      <c r="B19" s="15"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="14"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="37"/>
     </row>
     <row r="20" spans="2:6" ht="17.25" thickBot="1">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="40" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="18">
+      <c r="C20" s="41">
         <f>SUM(C3:C19)</f>
-        <v>1331251</v>
-      </c>
-      <c r="D20" s="18">
+        <v>1679874</v>
+      </c>
+      <c r="D20" s="41">
         <f t="shared" ref="D20:E20" si="0">SUM(D3:D19)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="18">
+      <c r="E20" s="41">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="19">
+      <c r="F20" s="42">
         <f>SUM(C20:E20)</f>
-        <v>1331251</v>
+        <v>1679874</v>
       </c>
     </row>
   </sheetData>
@@ -2177,7 +2263,7 @@
       <c r="D2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="20" t="s">
         <v>64</v>
       </c>
       <c r="G2" s="7" t="s">
@@ -2189,7 +2275,7 @@
       <c r="I2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="30" t="s">
+      <c r="J2" s="20" t="s">
         <v>64</v>
       </c>
       <c r="L2" s="7" t="s">
@@ -2201,25 +2287,25 @@
       <c r="N2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="O2" s="30" t="s">
+      <c r="O2" s="20" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="3" spans="2:15">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="29">
         <v>166640</v>
       </c>
-      <c r="D3" s="31"/>
-      <c r="E3" s="2">
+      <c r="D3" s="28"/>
+      <c r="E3" s="30">
         <v>1</v>
       </c>
-      <c r="G3" s="31" t="s">
+      <c r="G3" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="32">
+      <c r="H3" s="22">
         <v>99936</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2228,32 +2314,32 @@
       <c r="J3" s="2">
         <v>0</v>
       </c>
-      <c r="L3" s="31" t="s">
+      <c r="L3" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="M3" s="32">
+      <c r="M3" s="22">
         <v>233015</v>
       </c>
-      <c r="N3" s="31"/>
+      <c r="N3" s="21"/>
       <c r="O3" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="22">
         <v>251349</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2">
         <v>2</v>
       </c>
-      <c r="G4" s="31" t="s">
+      <c r="G4" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="32">
+      <c r="H4" s="22">
         <v>118730</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -2262,44 +2348,44 @@
       <c r="J4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="31" t="s">
+      <c r="L4" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="22">
         <v>236914</v>
       </c>
-      <c r="N4" s="31"/>
+      <c r="N4" s="21"/>
       <c r="O4" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:15">
-      <c r="G5" s="31" t="s">
+      <c r="G5" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="32">
+      <c r="H5" s="22">
         <v>135723</v>
       </c>
-      <c r="I5" s="31"/>
+      <c r="I5" s="21"/>
       <c r="J5" s="2">
         <v>2</v>
       </c>
-      <c r="L5" s="31" t="s">
+      <c r="L5" s="28" t="s">
         <v>47</v>
       </c>
-      <c r="M5" s="32">
+      <c r="M5" s="29">
         <v>195095</v>
       </c>
-      <c r="N5" s="31"/>
-      <c r="O5" s="2">
+      <c r="N5" s="28"/>
+      <c r="O5" s="30">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:15">
-      <c r="G6" s="31" t="s">
+      <c r="G6" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="32">
+      <c r="H6" s="22">
         <v>73378</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -2308,22 +2394,22 @@
       <c r="J6" s="2">
         <v>3</v>
       </c>
-      <c r="L6" s="31" t="s">
+      <c r="L6" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="M6" s="32">
+      <c r="M6" s="22">
         <v>234338</v>
       </c>
-      <c r="N6" s="31"/>
+      <c r="N6" s="21"/>
       <c r="O6" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:15">
-      <c r="G7" s="31" t="s">
+      <c r="G7" s="21" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="32">
+      <c r="H7" s="22">
         <v>138083</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -2334,22 +2420,22 @@
       </c>
     </row>
     <row r="8" spans="2:15">
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="32">
+      <c r="H8" s="22">
         <v>64817</v>
       </c>
-      <c r="I8" s="31"/>
+      <c r="I8" s="21"/>
       <c r="J8" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:15">
-      <c r="G9" s="31" t="s">
+      <c r="G9" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="32">
+      <c r="H9" s="22">
         <v>141342</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -2360,10 +2446,10 @@
       </c>
     </row>
     <row r="10" spans="2:15">
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="H10" s="32">
+      <c r="H10" s="22">
         <v>50353</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -2374,22 +2460,22 @@
       </c>
     </row>
     <row r="11" spans="2:15">
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="H11" s="32">
+      <c r="H11" s="22">
         <v>118334</v>
       </c>
-      <c r="I11" s="31"/>
+      <c r="I11" s="21"/>
       <c r="J11" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:15">
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="32">
+      <c r="H12" s="22">
         <v>104787</v>
       </c>
       <c r="I12" s="2" t="s">

--- a/travel/보홀/2026_보홀.xlsx
+++ b/travel/보홀/2026_보홀.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\보홀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF8CAE8C-F01A-4B5A-BC09-FFC42F907FD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DE4DB9-DE13-402E-A47E-50ED813E42C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
   <si>
     <t>토</t>
   </si>
@@ -72,14 +72,6 @@
   </si>
   <si>
     <t>금</t>
-  </si>
-  <si>
-    <t>세종 출발</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>인천공항 도착</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>원</t>
@@ -381,6 +373,67 @@
     <t>숙소(비그랜드리조트)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>21:59 서울 도착
+22:20 직통 공항철도 출발</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>23:03 인천공항 도착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5:20 인천</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:10 마닐라</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>07:15 광명역 도착
+07:27 광명역 출발 (ktx)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>21:04 오송 출발 (ktx)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>08:01 오송 도착</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">06:25 인천 공항버스 출발 (6004)
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>=&gt; 2주 전에 예매권 올라옴</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울-인천공항 공항철도</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>오송-서울 ktx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>광명-오송 ktx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -391,7 +444,7 @@
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
     <numFmt numFmtId="177" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +527,15 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -537,7 +599,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -761,6 +823,43 @@
         <color indexed="64"/>
       </diagonal>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -773,7 +872,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -867,6 +966,33 @@
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -876,32 +1002,20 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="20" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1136,6 +1250,50 @@
         <a:xfrm>
           <a:off x="733425" y="5676900"/>
           <a:ext cx="7505700" cy="6424292"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>87392</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BA77F46-14C4-46A8-D1D5-E06DC957F75A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8886825" y="5667375"/>
+          <a:ext cx="5343525" cy="3849767"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1468,15 +1626,17 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="11" width="25.625" customWidth="1"/>
+    <col min="3" max="3" width="30.875" customWidth="1"/>
+    <col min="4" max="10" width="25.625" customWidth="1"/>
+    <col min="11" max="11" width="30.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="45.75">
       <c r="A1" s="15" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -1553,8 +1713,8 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="11">
-        <v>0.50694444444444442</v>
+      <c r="K4" s="11" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="17.25" thickBot="1">
@@ -1569,9 +1729,7 @@
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3"/>
-      <c r="K5" s="14" t="s">
-        <v>17</v>
-      </c>
+      <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:13">
       <c r="B6" s="9">
@@ -1595,7 +1753,7 @@
       </c>
       <c r="C7" s="6"/>
       <c r="D7" s="14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
@@ -1619,7 +1777,7 @@
       <c r="J8" s="3"/>
       <c r="K8" s="5"/>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" ht="17.25" thickBot="1">
       <c r="B9" s="9">
         <v>0.20833333333333301</v>
       </c>
@@ -1633,29 +1791,29 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="11">
-        <v>0.22222222222222221</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="17.25" thickBot="1">
+      <c r="K9" s="46" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="33.75" thickBot="1">
       <c r="B10" s="9">
         <v>0.25</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="14" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="3"/>
-      <c r="K10" s="14" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="J10" s="45"/>
+      <c r="K10" s="47" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="33">
       <c r="B11" s="9">
         <v>0.29166666666666702</v>
       </c>
@@ -1667,7 +1825,9 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="5"/>
+      <c r="K11" s="44" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="12" spans="1:13" ht="17.25" thickBot="1">
       <c r="B12" s="9">
@@ -1681,7 +1841,9 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="5"/>
+      <c r="K12" s="5" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="13" spans="1:13">
       <c r="B13" s="9">
@@ -1705,7 +1867,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="12" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
@@ -1737,17 +1899,17 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="K16" s="5"/>
     </row>
@@ -1771,7 +1933,7 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1791,7 +1953,7 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -1857,9 +2019,7 @@
       <c r="B24" s="9">
         <v>0.83333333333333304</v>
       </c>
-      <c r="C24" s="6" t="s">
-        <v>8</v>
-      </c>
+      <c r="C24" s="6"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
       <c r="F24" s="3"/>
@@ -1874,7 +2034,9 @@
       <c r="B25" s="9">
         <v>0.875</v>
       </c>
-      <c r="C25" s="6"/>
+      <c r="C25" s="6" t="s">
+        <v>79</v>
+      </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
       <c r="F25" s="3"/>
@@ -1882,15 +2044,17 @@
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
       <c r="J25" s="12" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K25" s="5"/>
     </row>
-    <row r="26" spans="2:11">
+    <row r="26" spans="2:11" ht="33">
       <c r="B26" s="9">
         <v>0.91666666666666696</v>
       </c>
-      <c r="C26" s="6"/>
+      <c r="C26" s="43" t="s">
+        <v>74</v>
+      </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
       <c r="F26" s="3"/>
@@ -1907,7 +2071,7 @@
         <v>0.95833333333333304</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>9</v>
+        <v>75</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -1916,7 +2080,7 @@
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
       <c r="J27" s="25" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K27" s="5"/>
     </row>
@@ -1925,108 +2089,108 @@
         <v>1</v>
       </c>
       <c r="C28" s="23"/>
-      <c r="D28" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
+      <c r="D28" s="40" t="s">
+        <v>65</v>
+      </c>
+      <c r="E28" s="41"/>
+      <c r="F28" s="41"/>
+      <c r="G28" s="41"/>
       <c r="H28" s="27"/>
-      <c r="I28" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="J28" s="33"/>
+      <c r="I28" s="41" t="s">
+        <v>68</v>
+      </c>
+      <c r="J28" s="42"/>
       <c r="K28" s="24"/>
     </row>
     <row r="31" spans="2:11">
       <c r="C31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="2:11">
       <c r="C32" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="3:9">
       <c r="C33" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G33" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="I33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="34" spans="3:9">
       <c r="C34" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="3:9">
       <c r="C35" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D35" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E35" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="36" spans="3:9">
       <c r="C36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E36" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G36" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H36" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="3:9">
       <c r="D38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="40" spans="3:9">
       <c r="D40" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="42" spans="3:9">
       <c r="D42" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="46" spans="3:9" ht="36">
       <c r="D46" s="16" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="3:9" ht="36">
       <c r="D47" s="17" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="48" spans="3:9" ht="36">
       <c r="D48" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49" spans="4:4" ht="54">
       <c r="D49" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="50" spans="4:4" ht="33.75">
       <c r="D50" s="18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -2045,7 +2209,7 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
-    <col min="2" max="2" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="9.125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.125" customWidth="1"/>
@@ -2054,166 +2218,178 @@
     <row r="2" spans="2:6">
       <c r="B2" s="26"/>
       <c r="C2" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="26" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="F2" s="31"/>
+    </row>
+    <row r="3" spans="2:6">
+      <c r="B3" s="32" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="C3" s="33">
+        <v>985619</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="F3" s="34"/>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C4" s="33">
+        <v>345632</v>
+      </c>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="34"/>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" s="33">
+        <v>348623</v>
+      </c>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="34"/>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="33">
+        <v>23000</v>
+      </c>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="34"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="33">
+        <v>37000</v>
+      </c>
+      <c r="D7" s="33"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="34"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" s="33">
+        <v>32200</v>
+      </c>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="34"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="32"/>
+      <c r="C9" s="33"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="34"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="32"/>
+      <c r="C10" s="33"/>
+      <c r="D10" s="33"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="34"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="32"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="34"/>
+    </row>
+    <row r="12" spans="2:6">
+      <c r="B12" s="32"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="34"/>
+    </row>
+    <row r="13" spans="2:6">
+      <c r="B13" s="32"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="34"/>
+    </row>
+    <row r="14" spans="2:6">
+      <c r="B14" s="32"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="33"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="34"/>
+    </row>
+    <row r="15" spans="2:6">
+      <c r="B15" s="32"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="34"/>
+    </row>
+    <row r="16" spans="2:6">
+      <c r="B16" s="32"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="34"/>
+    </row>
+    <row r="17" spans="2:6">
+      <c r="B17" s="32"/>
+      <c r="C17" s="33"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="34"/>
+    </row>
+    <row r="18" spans="2:6">
+      <c r="B18" s="32"/>
+      <c r="C18" s="33"/>
+      <c r="D18" s="33"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="34"/>
+    </row>
+    <row r="19" spans="2:6" ht="17.25" thickBot="1">
+      <c r="B19" s="35"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="34"/>
+    </row>
+    <row r="20" spans="2:6" ht="17.25" thickBot="1">
+      <c r="B20" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="F2" s="34"/>
-    </row>
-    <row r="3" spans="2:6">
-      <c r="B3" s="35" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="36">
-        <v>985619</v>
-      </c>
-      <c r="D3" s="36"/>
-      <c r="E3" s="36"/>
-      <c r="F3" s="37"/>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C4" s="36">
-        <v>345632</v>
-      </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="37"/>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" s="36">
-        <v>348623</v>
-      </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" s="37"/>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="35"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="37"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="35"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="35"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="37"/>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="35"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="37"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="35"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="37"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="35"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" s="37"/>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" s="35"/>
-      <c r="C12" s="36"/>
-      <c r="D12" s="36"/>
-      <c r="E12" s="36"/>
-      <c r="F12" s="37"/>
-    </row>
-    <row r="13" spans="2:6">
-      <c r="B13" s="35"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="37"/>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" s="35"/>
-      <c r="C14" s="36"/>
-      <c r="D14" s="36"/>
-      <c r="E14" s="36"/>
-      <c r="F14" s="37"/>
-    </row>
-    <row r="15" spans="2:6">
-      <c r="B15" s="35"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="37"/>
-    </row>
-    <row r="16" spans="2:6">
-      <c r="B16" s="35"/>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="E16" s="36"/>
-      <c r="F16" s="37"/>
-    </row>
-    <row r="17" spans="2:6">
-      <c r="B17" s="35"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="36"/>
-      <c r="F17" s="37"/>
-    </row>
-    <row r="18" spans="2:6">
-      <c r="B18" s="35"/>
-      <c r="C18" s="36"/>
-      <c r="D18" s="36"/>
-      <c r="E18" s="36"/>
-      <c r="F18" s="37"/>
-    </row>
-    <row r="19" spans="2:6" ht="17.25" thickBot="1">
-      <c r="B19" s="38"/>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
-      <c r="F19" s="37"/>
-    </row>
-    <row r="20" spans="2:6" ht="17.25" thickBot="1">
-      <c r="B20" s="40" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="41">
+      <c r="C20" s="38">
         <f>SUM(C3:C19)</f>
-        <v>1679874</v>
-      </c>
-      <c r="D20" s="41">
+        <v>1772074</v>
+      </c>
+      <c r="D20" s="38">
         <f t="shared" ref="D20:E20" si="0">SUM(D3:D19)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="41">
+      <c r="E20" s="38">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="F20" s="42">
+      <c r="F20" s="39">
         <f>SUM(C20:E20)</f>
-        <v>1679874</v>
+        <v>1772074</v>
       </c>
     </row>
   </sheetData>
@@ -2255,45 +2431,45 @@
   <sheetData>
     <row r="2" spans="2:15">
       <c r="B2" s="7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="J2" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="L2" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="M2" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="O2" s="20" t="s">
         <v>62</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="J2" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="O2" s="20" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="3" spans="2:15">
       <c r="B3" s="28" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C3" s="29">
         <v>166640</v>
@@ -2303,19 +2479,19 @@
         <v>1</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H3" s="22">
         <v>99936</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J3" s="2">
         <v>0</v>
       </c>
       <c r="L3" s="21" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M3" s="22">
         <v>233015</v>
@@ -2327,7 +2503,7 @@
     </row>
     <row r="4" spans="2:15">
       <c r="B4" s="21" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C4" s="22">
         <v>251349</v>
@@ -2337,19 +2513,19 @@
         <v>2</v>
       </c>
       <c r="G4" s="21" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="H4" s="22">
         <v>118730</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J4" s="2">
         <v>1</v>
       </c>
       <c r="L4" s="21" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M4" s="22">
         <v>236914</v>
@@ -2361,7 +2537,7 @@
     </row>
     <row r="5" spans="2:15">
       <c r="G5" s="21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H5" s="22">
         <v>135723</v>
@@ -2371,7 +2547,7 @@
         <v>2</v>
       </c>
       <c r="L5" s="28" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M5" s="29">
         <v>195095</v>
@@ -2383,19 +2559,19 @@
     </row>
     <row r="6" spans="2:15">
       <c r="G6" s="21" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H6" s="22">
         <v>73378</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J6" s="2">
         <v>3</v>
       </c>
       <c r="L6" s="21" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M6" s="22">
         <v>234338</v>
@@ -2407,13 +2583,13 @@
     </row>
     <row r="7" spans="2:15">
       <c r="G7" s="21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="H7" s="22">
         <v>138083</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="J7" s="2">
         <v>4</v>
@@ -2421,7 +2597,7 @@
     </row>
     <row r="8" spans="2:15">
       <c r="G8" s="21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H8" s="22">
         <v>64817</v>
@@ -2433,13 +2609,13 @@
     </row>
     <row r="9" spans="2:15">
       <c r="G9" s="21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H9" s="22">
         <v>141342</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J9" s="2">
         <v>6</v>
@@ -2447,13 +2623,13 @@
     </row>
     <row r="10" spans="2:15">
       <c r="G10" s="21" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="H10" s="22">
         <v>50353</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J10" s="2">
         <v>7</v>
@@ -2461,7 +2637,7 @@
     </row>
     <row r="11" spans="2:15">
       <c r="G11" s="21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H11" s="22">
         <v>118334</v>
@@ -2473,13 +2649,13 @@
     </row>
     <row r="12" spans="2:15">
       <c r="G12" s="21" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H12" s="22">
         <v>104787</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="J12" s="2">
         <v>9</v>

--- a/travel/보홀/2026_보홀.xlsx
+++ b/travel/보홀/2026_보홀.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\보홀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9DE4DB9-DE13-402E-A47E-50ED813E42C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7023CAB-56EA-406D-A3D4-7289CBD787F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
   <si>
     <t>토</t>
   </si>
@@ -432,6 +432,10 @@
   </si>
   <si>
     <t>광명-오송 ktx</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>필리핀 eSIM</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -993,15 +997,6 @@
     <xf numFmtId="41" fontId="2" fillId="6" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1016,6 +1011,15 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1294,6 +1298,50 @@
         <a:xfrm>
           <a:off x="8886825" y="5667375"/>
           <a:ext cx="5343525" cy="3849767"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>447674</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>2451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>592471</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>39265</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="그림 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{130F92DF-C149-7FB1-08BA-F9871CB03F02}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14849474" y="5660301"/>
+          <a:ext cx="9745997" cy="5904214"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1791,7 +1839,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="46" t="s">
+      <c r="K9" s="43" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1808,8 +1856,8 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
-      <c r="J10" s="45"/>
-      <c r="K10" s="47" t="s">
+      <c r="J10" s="42"/>
+      <c r="K10" s="44" t="s">
         <v>81</v>
       </c>
     </row>
@@ -1825,7 +1873,7 @@
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="44" t="s">
+      <c r="K11" s="41" t="s">
         <v>78</v>
       </c>
     </row>
@@ -2052,7 +2100,7 @@
       <c r="B26" s="9">
         <v>0.91666666666666696</v>
       </c>
-      <c r="C26" s="43" t="s">
+      <c r="C26" s="40" t="s">
         <v>74</v>
       </c>
       <c r="D26" s="3"/>
@@ -2089,17 +2137,17 @@
         <v>1</v>
       </c>
       <c r="C28" s="23"/>
-      <c r="D28" s="40" t="s">
+      <c r="D28" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="41"/>
-      <c r="F28" s="41"/>
-      <c r="G28" s="41"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="46"/>
       <c r="H28" s="27"/>
-      <c r="I28" s="41" t="s">
+      <c r="I28" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="J28" s="42"/>
+      <c r="J28" s="47"/>
       <c r="K28" s="24"/>
     </row>
     <row r="31" spans="2:11">
@@ -2295,8 +2343,12 @@
       <c r="F8" s="34"/>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="32"/>
-      <c r="C9" s="33"/>
+      <c r="B9" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C9" s="33">
+        <v>9618</v>
+      </c>
       <c r="D9" s="33"/>
       <c r="E9" s="33"/>
       <c r="F9" s="34"/>
@@ -2377,7 +2429,7 @@
       </c>
       <c r="C20" s="38">
         <f>SUM(C3:C19)</f>
-        <v>1772074</v>
+        <v>1781692</v>
       </c>
       <c r="D20" s="38">
         <f t="shared" ref="D20:E20" si="0">SUM(D3:D19)</f>
@@ -2389,7 +2441,7 @@
       </c>
       <c r="F20" s="39">
         <f>SUM(C20:E20)</f>
-        <v>1772074</v>
+        <v>1781692</v>
       </c>
     </row>
   </sheetData>

--- a/travel/보홀/2026_보홀.xlsx
+++ b/travel/보홀/2026_보홀.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\보홀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7023CAB-56EA-406D-A3D4-7289CBD787F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3D2F6E-BFA4-41EF-BC96-4020C708709A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
@@ -404,25 +404,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">06:25 인천 공항버스 출발 (6004)
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>=&gt; 2주 전에 예매권 올라옴</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>서울-인천공항 공항철도</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -436,6 +417,10 @@
   </si>
   <si>
     <t>필리핀 eSIM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>06:25 인천 공항버스 출발 (티머니go)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -448,7 +433,7 @@
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
     <numFmt numFmtId="177" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -531,15 +516,6 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="11">
     <fill>
@@ -603,7 +579,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="20">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -846,21 +822,8 @@
       <top style="medium">
         <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFFF0000"/>
-      </top>
       <bottom style="medium">
-        <color rgb="FFFF0000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -876,7 +839,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1006,19 +969,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="20" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1088,50 +1048,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>666751</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>20674</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2D49E2A-9F9D-8689-D537-2546A613A095}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5505451" y="209550"/>
-          <a:ext cx="2705100" cy="5259424"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>13</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
@@ -1157,7 +1073,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1201,7 +1117,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1245,7 +1161,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1289,7 +1205,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1333,7 +1249,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1342,6 +1258,138 @@
         <a:xfrm>
           <a:off x="14849474" y="5660301"/>
           <a:ext cx="9745997" cy="5904214"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>651219</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="그림 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2D49E2A-9F9D-8689-D537-2546A613A095}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5505451" y="209550"/>
+          <a:ext cx="2689568" cy="5229225"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>676276</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>529611</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>139752</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{943356FA-9075-CD5E-7441-A281F14538DC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8905876" y="9791700"/>
+          <a:ext cx="2596535" cy="5645202"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>575771</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>413018</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="그림 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0661B66B-8BA8-3856-3350-3FCF1043B758}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11548571" y="9801225"/>
+          <a:ext cx="2580447" cy="5610225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1676,7 +1724,7 @@
     <col min="2" max="2" width="5.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="30.875" customWidth="1"/>
     <col min="4" max="10" width="25.625" customWidth="1"/>
-    <col min="11" max="11" width="30.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="45.75">
@@ -1749,7 +1797,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" ht="17.25" thickBot="1">
       <c r="B4" s="9">
         <v>0</v>
       </c>
@@ -1761,7 +1809,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="46" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1839,11 +1887,11 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="43" t="s">
+      <c r="K9" s="46" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="33.75" thickBot="1">
+    <row r="10" spans="1:13" ht="17.25" thickBot="1">
       <c r="B10" s="9">
         <v>0.25</v>
       </c>
@@ -1857,8 +1905,8 @@
       <c r="H10" s="3"/>
       <c r="I10" s="3"/>
       <c r="J10" s="42"/>
-      <c r="K10" s="44" t="s">
-        <v>81</v>
+      <c r="K10" s="5" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="33">
@@ -2137,17 +2185,17 @@
         <v>1</v>
       </c>
       <c r="C28" s="23"/>
-      <c r="D28" s="45" t="s">
+      <c r="D28" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="46"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
       <c r="H28" s="27"/>
-      <c r="I28" s="46" t="s">
+      <c r="I28" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="J28" s="47"/>
+      <c r="J28" s="45"/>
       <c r="K28" s="24"/>
     </row>
     <row r="31" spans="2:11">
@@ -2311,7 +2359,7 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="32" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C6" s="33">
         <v>23000</v>
@@ -2322,7 +2370,7 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="32" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C7" s="33">
         <v>37000</v>
@@ -2333,7 +2381,7 @@
     </row>
     <row r="8" spans="2:6">
       <c r="B8" s="32" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="33">
         <v>32200</v>
@@ -2344,7 +2392,7 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" s="32" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" s="33">
         <v>9618</v>

--- a/travel/보홀/2026_보홀.xlsx
+++ b/travel/보홀/2026_보홀.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\보홀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE3D2F6E-BFA4-41EF-BC96-4020C708709A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D47E0FB-C6C0-4802-ADAA-29ADFD72641F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
   <si>
     <t>토</t>
   </si>
@@ -421,6 +421,22 @@
   </si>
   <si>
     <t>06:25 인천 공항버스 출발 (티머니go)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현지인 투어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>육지 투어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국 투어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>인천공항-광명 공항버스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -969,6 +985,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -976,9 +995,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1809,7 +1825,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3"/>
-      <c r="K4" s="46" t="s">
+      <c r="K4" s="43" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1835,9 +1851,15 @@
       <c r="D6" s="11">
         <v>9.375E-2</v>
       </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
+      <c r="E6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3"/>
@@ -1887,7 +1909,7 @@
       <c r="H9" s="3"/>
       <c r="I9" s="3"/>
       <c r="J9" s="3"/>
-      <c r="K9" s="46" t="s">
+      <c r="K9" s="43" t="s">
         <v>76</v>
       </c>
     </row>
@@ -2185,17 +2207,17 @@
         <v>1</v>
       </c>
       <c r="C28" s="23"/>
-      <c r="D28" s="43" t="s">
+      <c r="D28" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
       <c r="H28" s="27"/>
-      <c r="I28" s="44" t="s">
+      <c r="I28" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="J28" s="45"/>
+      <c r="J28" s="46"/>
       <c r="K28" s="24"/>
     </row>
     <row r="31" spans="2:11">
@@ -2402,8 +2424,12 @@
       <c r="F9" s="34"/>
     </row>
     <row r="10" spans="2:6">
-      <c r="B10" s="32"/>
-      <c r="C10" s="33"/>
+      <c r="B10" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C10" s="33">
+        <v>32000</v>
+      </c>
       <c r="D10" s="33"/>
       <c r="E10" s="33"/>
       <c r="F10" s="34"/>
@@ -2477,7 +2503,7 @@
       </c>
       <c r="C20" s="38">
         <f>SUM(C3:C19)</f>
-        <v>1781692</v>
+        <v>1813692</v>
       </c>
       <c r="D20" s="38">
         <f t="shared" ref="D20:E20" si="0">SUM(D3:D19)</f>
@@ -2489,7 +2515,7 @@
       </c>
       <c r="F20" s="39">
         <f>SUM(C20:E20)</f>
-        <v>1781692</v>
+        <v>1813692</v>
       </c>
     </row>
   </sheetData>

--- a/travel/보홀/2026_보홀.xlsx
+++ b/travel/보홀/2026_보홀.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\보홀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D47E0FB-C6C0-4802-ADAA-29ADFD72641F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4732DCB9-B163-4870-AADC-40214092C0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
   <si>
     <t>토</t>
   </si>
@@ -428,15 +428,27 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>육지 투어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한국 투어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>인천공항-광명 공항버스</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>초콜릿힐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>안경원숭이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한국 투어 (한바다 호핑)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>로복강 투어 (점심)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>육상 현지 투어 (반나절)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -855,7 +867,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -982,9 +994,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="20" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -995,6 +1004,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1819,13 +1834,13 @@
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
-      <c r="J4" s="3"/>
-      <c r="K4" s="43" t="s">
+      <c r="E4" s="46"/>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
+      <c r="I4" s="46"/>
+      <c r="J4" s="46"/>
+      <c r="K4" s="42" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1835,12 +1850,12 @@
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3"/>
+      <c r="E5" s="46"/>
+      <c r="F5" s="46"/>
+      <c r="G5" s="46"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
+      <c r="J5" s="46"/>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:13">
@@ -1851,18 +1866,12 @@
       <c r="D6" s="11">
         <v>9.375E-2</v>
       </c>
-      <c r="E6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
-      <c r="J6" s="3"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:13" ht="17.25" thickBot="1">
@@ -1873,12 +1882,12 @@
       <c r="D7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3"/>
+      <c r="E7" s="46"/>
+      <c r="F7" s="46"/>
+      <c r="G7" s="46"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
+      <c r="J7" s="46"/>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:13" ht="17.25" thickBot="1">
@@ -1887,12 +1896,12 @@
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
-      <c r="J8" s="3"/>
+      <c r="E8" s="46"/>
+      <c r="F8" s="46"/>
+      <c r="G8" s="46"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
+      <c r="J8" s="46"/>
       <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:13" ht="17.25" thickBot="1">
@@ -1903,13 +1912,13 @@
       <c r="D9" s="11">
         <v>0.2361111111111111</v>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3"/>
-      <c r="K9" s="43" t="s">
+      <c r="E9" s="46"/>
+      <c r="F9" s="46"/>
+      <c r="G9" s="46"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
+      <c r="J9" s="46"/>
+      <c r="K9" s="42" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1921,12 +1930,12 @@
       <c r="D10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
-      <c r="J10" s="42"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="46"/>
+      <c r="G10" s="46"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
+      <c r="J10" s="47"/>
       <c r="K10" s="5" t="s">
         <v>85</v>
       </c>
@@ -1937,12 +1946,12 @@
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3"/>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="46"/>
+      <c r="G11" s="46"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
+      <c r="J11" s="46"/>
       <c r="K11" s="41" t="s">
         <v>78</v>
       </c>
@@ -1953,12 +1962,12 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
-      <c r="J12" s="3"/>
+      <c r="E12" s="46"/>
+      <c r="F12" s="46"/>
+      <c r="G12" s="46"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
+      <c r="J12" s="46"/>
       <c r="K12" s="5" t="s">
         <v>80</v>
       </c>
@@ -1971,9 +1980,15 @@
       <c r="D13" s="11">
         <v>0.39930555555555558</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+      <c r="E13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>90</v>
+      </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
@@ -1988,7 +2003,9 @@
         <v>15</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="F14" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
@@ -2004,7 +2021,9 @@
         <v>0.47222222222222221</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="F15" s="3" t="s">
+        <v>89</v>
+      </c>
       <c r="G15" s="3"/>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -2020,7 +2039,9 @@
         <v>14</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="F16" s="3" t="s">
+        <v>91</v>
+      </c>
       <c r="G16" s="3"/>
       <c r="H16" s="3" t="s">
         <v>70</v>
@@ -2207,17 +2228,17 @@
         <v>1</v>
       </c>
       <c r="C28" s="23"/>
-      <c r="D28" s="44" t="s">
+      <c r="D28" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
+      <c r="E28" s="44"/>
+      <c r="F28" s="44"/>
+      <c r="G28" s="44"/>
       <c r="H28" s="27"/>
-      <c r="I28" s="45" t="s">
+      <c r="I28" s="44" t="s">
         <v>68</v>
       </c>
-      <c r="J28" s="46"/>
+      <c r="J28" s="45"/>
       <c r="K28" s="24"/>
     </row>
     <row r="31" spans="2:11">
@@ -2425,7 +2446,7 @@
     </row>
     <row r="10" spans="2:6">
       <c r="B10" s="32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C10" s="33">
         <v>32000</v>

--- a/travel/보홀/2026_보홀.xlsx
+++ b/travel/보홀/2026_보홀.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\보홀\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\csw\travel\보홀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4732DCB9-B163-4870-AADC-40214092C0DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BFC745-BEFE-45BE-9F64-19ACB1F67A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
@@ -37,15 +37,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="95">
   <si>
     <t>토</t>
   </si>
@@ -449,6 +446,14 @@
   </si>
   <si>
     <t>육상 현지 투어 (반나절)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한바다 투어</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>환율</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -545,7 +550,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -606,6 +611,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -928,9 +939,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -949,7 +957,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -997,6 +1005,12 @@
     <xf numFmtId="20" fontId="0" fillId="7" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1006,10 +1020,7 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1834,13 +1845,13 @@
       </c>
       <c r="C4" s="6"/>
       <c r="D4" s="5"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="42" t="s">
+      <c r="E4" s="42"/>
+      <c r="F4" s="42"/>
+      <c r="G4" s="42"/>
+      <c r="H4" s="42"/>
+      <c r="I4" s="42"/>
+      <c r="J4" s="42"/>
+      <c r="K4" s="41" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1850,12 +1861,12 @@
       </c>
       <c r="C5" s="6"/>
       <c r="D5" s="5"/>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
-      <c r="J5" s="46"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="42"/>
       <c r="K5" s="5"/>
     </row>
     <row r="6" spans="1:13">
@@ -1866,12 +1877,12 @@
       <c r="D6" s="11">
         <v>9.375E-2</v>
       </c>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="42"/>
+      <c r="G6" s="42"/>
+      <c r="H6" s="42"/>
+      <c r="I6" s="42"/>
+      <c r="J6" s="42"/>
       <c r="K6" s="5"/>
     </row>
     <row r="7" spans="1:13" ht="17.25" thickBot="1">
@@ -1882,12 +1893,12 @@
       <c r="D7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="46"/>
-      <c r="F7" s="46"/>
-      <c r="G7" s="46"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
-      <c r="J7" s="46"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="42"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
       <c r="K7" s="5"/>
     </row>
     <row r="8" spans="1:13" ht="17.25" thickBot="1">
@@ -1896,12 +1907,12 @@
       </c>
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
-      <c r="E8" s="46"/>
-      <c r="F8" s="46"/>
-      <c r="G8" s="46"/>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
-      <c r="J8" s="46"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
+      <c r="H8" s="42"/>
+      <c r="I8" s="42"/>
+      <c r="J8" s="42"/>
       <c r="K8" s="5"/>
     </row>
     <row r="9" spans="1:13" ht="17.25" thickBot="1">
@@ -1912,13 +1923,13 @@
       <c r="D9" s="11">
         <v>0.2361111111111111</v>
       </c>
-      <c r="E9" s="46"/>
-      <c r="F9" s="46"/>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
-      <c r="J9" s="46"/>
-      <c r="K9" s="42" t="s">
+      <c r="E9" s="42"/>
+      <c r="F9" s="42"/>
+      <c r="G9" s="42"/>
+      <c r="H9" s="42"/>
+      <c r="I9" s="42"/>
+      <c r="J9" s="42"/>
+      <c r="K9" s="41" t="s">
         <v>76</v>
       </c>
     </row>
@@ -1930,12 +1941,12 @@
       <c r="D10" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="46"/>
-      <c r="F10" s="46"/>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="47"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="42"/>
+      <c r="G10" s="42"/>
+      <c r="H10" s="42"/>
+      <c r="I10" s="42"/>
+      <c r="J10" s="43"/>
       <c r="K10" s="5" t="s">
         <v>85</v>
       </c>
@@ -1946,13 +1957,13 @@
       </c>
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
-      <c r="E11" s="46"/>
-      <c r="F11" s="46"/>
-      <c r="G11" s="46"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="46"/>
-      <c r="K11" s="41" t="s">
+      <c r="E11" s="42"/>
+      <c r="F11" s="42"/>
+      <c r="G11" s="42"/>
+      <c r="H11" s="42"/>
+      <c r="I11" s="42"/>
+      <c r="J11" s="42"/>
+      <c r="K11" s="40" t="s">
         <v>78</v>
       </c>
     </row>
@@ -1962,12 +1973,12 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="46"/>
-      <c r="G12" s="46"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
-      <c r="J12" s="46"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="42"/>
+      <c r="G12" s="42"/>
+      <c r="H12" s="42"/>
+      <c r="I12" s="42"/>
+      <c r="J12" s="42"/>
       <c r="K12" s="5" t="s">
         <v>80</v>
       </c>
@@ -2191,7 +2202,7 @@
       <c r="B26" s="9">
         <v>0.91666666666666696</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="39" t="s">
         <v>74</v>
       </c>
       <c r="D26" s="3"/>
@@ -2218,7 +2229,7 @@
       <c r="G27" s="3"/>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="25" t="s">
+      <c r="J27" s="24" t="s">
         <v>15</v>
       </c>
       <c r="K27" s="5"/>
@@ -2227,19 +2238,19 @@
       <c r="B28" s="10">
         <v>1</v>
       </c>
-      <c r="C28" s="23"/>
-      <c r="D28" s="43" t="s">
+      <c r="C28" s="22"/>
+      <c r="D28" s="44" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="27"/>
-      <c r="I28" s="44" t="s">
+      <c r="E28" s="45"/>
+      <c r="F28" s="45"/>
+      <c r="G28" s="45"/>
+      <c r="H28" s="26"/>
+      <c r="I28" s="45" t="s">
         <v>68</v>
       </c>
-      <c r="J28" s="45"/>
-      <c r="K28" s="24"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="23"/>
     </row>
     <row r="31" spans="2:11">
       <c r="C31" t="s">
@@ -2339,209 +2350,321 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B29DE7-3267-4196-8A3E-54333E9A8DE2}">
-  <dimension ref="B2:F20"/>
+  <dimension ref="B2:F33"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
     <col min="2" max="2" width="22.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6">
-      <c r="B2" s="26"/>
-      <c r="C2" s="26" t="s">
+      <c r="B2" s="25"/>
+      <c r="C2" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="26" t="s">
+      <c r="D2" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="26" t="s">
+      <c r="E2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="30"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="C3" s="47">
+        <v>1</v>
+      </c>
+      <c r="D3" s="47">
+        <v>1470.5</v>
+      </c>
+      <c r="E3" s="47">
+        <v>23.84</v>
+      </c>
+      <c r="F3" s="30"/>
+    </row>
+    <row r="4" spans="2:6">
+      <c r="B4" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C4" s="32">
         <v>985619</v>
       </c>
-      <c r="D3" s="33"/>
-      <c r="E3" s="33"/>
-      <c r="F3" s="34"/>
-    </row>
-    <row r="4" spans="2:6">
-      <c r="B4" s="32" t="s">
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="33"/>
+    </row>
+    <row r="5" spans="2:6">
+      <c r="B5" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C5" s="32">
         <v>345632</v>
       </c>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="34"/>
-    </row>
-    <row r="5" spans="2:6">
-      <c r="B5" s="32" t="s">
+      <c r="D5" s="32"/>
+      <c r="E5" s="32"/>
+      <c r="F5" s="33"/>
+    </row>
+    <row r="6" spans="2:6">
+      <c r="B6" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C6" s="32">
         <v>348623</v>
       </c>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="34"/>
-    </row>
-    <row r="6" spans="2:6">
-      <c r="B6" s="32" t="s">
+      <c r="D6" s="32"/>
+      <c r="E6" s="32"/>
+      <c r="F6" s="33"/>
+    </row>
+    <row r="7" spans="2:6">
+      <c r="B7" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C7" s="32">
         <v>23000</v>
       </c>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="34"/>
-    </row>
-    <row r="7" spans="2:6">
-      <c r="B7" s="32" t="s">
+      <c r="D7" s="32"/>
+      <c r="E7" s="32"/>
+      <c r="F7" s="33"/>
+    </row>
+    <row r="8" spans="2:6">
+      <c r="B8" s="31" t="s">
         <v>82</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C8" s="32">
         <v>37000</v>
       </c>
-      <c r="D7" s="33"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="34"/>
-    </row>
-    <row r="8" spans="2:6">
-      <c r="B8" s="32" t="s">
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="33"/>
+    </row>
+    <row r="9" spans="2:6">
+      <c r="B9" s="31" t="s">
         <v>83</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C9" s="32">
         <v>32200</v>
       </c>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="34"/>
-    </row>
-    <row r="9" spans="2:6">
-      <c r="B9" s="32" t="s">
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="33"/>
+    </row>
+    <row r="10" spans="2:6">
+      <c r="B10" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C10" s="32">
         <v>9618</v>
       </c>
-      <c r="D9" s="33"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="34"/>
-    </row>
-    <row r="10" spans="2:6">
-      <c r="B10" s="32" t="s">
+      <c r="D10" s="32"/>
+      <c r="E10" s="32"/>
+      <c r="F10" s="33"/>
+    </row>
+    <row r="11" spans="2:6">
+      <c r="B11" s="31" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C11" s="32">
         <v>32000</v>
       </c>
-      <c r="D10" s="33"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="34"/>
-    </row>
-    <row r="11" spans="2:6">
-      <c r="B11" s="32"/>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="34"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
+      <c r="F11" s="33"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="32"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="34"/>
+      <c r="B12" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="32">
+        <v>40000</v>
+      </c>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32">
+        <v>6000</v>
+      </c>
+      <c r="F12" s="33"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="32"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="34"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="33"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="32"/>
-      <c r="C14" s="33"/>
-      <c r="D14" s="33"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="34"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="33"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="32"/>
-      <c r="C15" s="33"/>
-      <c r="D15" s="33"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="34"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="32"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="33"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="32"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="34"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="33"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="32"/>
-      <c r="C17" s="33"/>
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="34"/>
+      <c r="B17" s="31"/>
+      <c r="C17" s="32"/>
+      <c r="D17" s="32"/>
+      <c r="E17" s="32"/>
+      <c r="F17" s="33"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="32"/>
-      <c r="C18" s="33"/>
-      <c r="D18" s="33"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="34"/>
-    </row>
-    <row r="19" spans="2:6" ht="17.25" thickBot="1">
-      <c r="B19" s="35"/>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="34"/>
-    </row>
-    <row r="20" spans="2:6" ht="17.25" thickBot="1">
-      <c r="B20" s="37" t="s">
+      <c r="B18" s="31"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="33"/>
+    </row>
+    <row r="19" spans="2:6">
+      <c r="B19" s="31"/>
+      <c r="C19" s="32"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="32"/>
+      <c r="F19" s="33"/>
+    </row>
+    <row r="20" spans="2:6">
+      <c r="B20" s="31"/>
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32"/>
+      <c r="F20" s="33"/>
+    </row>
+    <row r="21" spans="2:6">
+      <c r="B21" s="31"/>
+      <c r="C21" s="32"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="33"/>
+    </row>
+    <row r="22" spans="2:6">
+      <c r="B22" s="31"/>
+      <c r="C22" s="32"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="32"/>
+      <c r="F22" s="33"/>
+    </row>
+    <row r="23" spans="2:6">
+      <c r="B23" s="31"/>
+      <c r="C23" s="32"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="33"/>
+    </row>
+    <row r="24" spans="2:6">
+      <c r="B24" s="31"/>
+      <c r="C24" s="32"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="33"/>
+    </row>
+    <row r="25" spans="2:6">
+      <c r="B25" s="31"/>
+      <c r="C25" s="32"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="32"/>
+      <c r="F25" s="33"/>
+    </row>
+    <row r="26" spans="2:6">
+      <c r="B26" s="31"/>
+      <c r="C26" s="32"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="32"/>
+      <c r="F26" s="33"/>
+    </row>
+    <row r="27" spans="2:6">
+      <c r="B27" s="31"/>
+      <c r="C27" s="32"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="33"/>
+    </row>
+    <row r="28" spans="2:6">
+      <c r="B28" s="31"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="33"/>
+    </row>
+    <row r="29" spans="2:6">
+      <c r="B29" s="31"/>
+      <c r="C29" s="32"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="32"/>
+      <c r="F29" s="33"/>
+    </row>
+    <row r="30" spans="2:6">
+      <c r="B30" s="31"/>
+      <c r="C30" s="32"/>
+      <c r="D30" s="32"/>
+      <c r="E30" s="32"/>
+      <c r="F30" s="33"/>
+    </row>
+    <row r="31" spans="2:6">
+      <c r="B31" s="31"/>
+      <c r="C31" s="32"/>
+      <c r="D31" s="32"/>
+      <c r="E31" s="32"/>
+      <c r="F31" s="33"/>
+    </row>
+    <row r="32" spans="2:6" ht="17.25" thickBot="1">
+      <c r="B32" s="34"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="33"/>
+    </row>
+    <row r="33" spans="2:6" ht="17.25" thickBot="1">
+      <c r="B33" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="38">
-        <f>SUM(C3:C19)</f>
-        <v>1813692</v>
-      </c>
-      <c r="D20" s="38">
-        <f t="shared" ref="D20:E20" si="0">SUM(D3:D19)</f>
+      <c r="C33" s="37">
+        <f>SUM(C4:C32)*C3</f>
+        <v>1853692</v>
+      </c>
+      <c r="D33" s="37">
+        <f>SUM(D4:D32)*D3</f>
         <v>0</v>
       </c>
-      <c r="E20" s="38">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="F20" s="39">
-        <f>SUM(C20:E20)</f>
-        <v>1813692</v>
+      <c r="E33" s="37">
+        <f>SUM(E4:E32)*E3</f>
+        <v>143040</v>
+      </c>
+      <c r="F33" s="38">
+        <f>SUM(C33:E33)</f>
+        <v>1996732</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Internal</oddFooter>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2552,6 +2675,9 @@
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Internal</oddFooter>
+  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -2586,7 +2712,7 @@
       <c r="D2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="E2" s="7" t="s">
         <v>62</v>
       </c>
       <c r="G2" s="7" t="s">
@@ -2598,7 +2724,7 @@
       <c r="I2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="J2" s="7" t="s">
         <v>62</v>
       </c>
       <c r="L2" s="7" t="s">
@@ -2610,25 +2736,25 @@
       <c r="N2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="7" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="3" spans="2:15">
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="27" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="29">
+      <c r="C3" s="28">
         <v>166640</v>
       </c>
-      <c r="D3" s="28"/>
-      <c r="E3" s="30">
+      <c r="D3" s="27"/>
+      <c r="E3" s="29">
         <v>1</v>
       </c>
-      <c r="G3" s="21" t="s">
+      <c r="G3" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="21">
         <v>99936</v>
       </c>
       <c r="I3" s="2" t="s">
@@ -2637,32 +2763,32 @@
       <c r="J3" s="2">
         <v>0</v>
       </c>
-      <c r="L3" s="21" t="s">
+      <c r="L3" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="M3" s="22">
+      <c r="M3" s="21">
         <v>233015</v>
       </c>
-      <c r="N3" s="21"/>
+      <c r="N3" s="20"/>
       <c r="O3" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="4" spans="2:15">
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="22">
+      <c r="C4" s="21">
         <v>251349</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2">
         <v>2</v>
       </c>
-      <c r="G4" s="21" t="s">
+      <c r="G4" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="21">
         <v>118730</v>
       </c>
       <c r="I4" s="2" t="s">
@@ -2671,44 +2797,44 @@
       <c r="J4" s="2">
         <v>1</v>
       </c>
-      <c r="L4" s="21" t="s">
+      <c r="L4" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="M4" s="22">
+      <c r="M4" s="21">
         <v>236914</v>
       </c>
-      <c r="N4" s="21"/>
+      <c r="N4" s="20"/>
       <c r="O4" s="2">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="2:15">
-      <c r="G5" s="21" t="s">
+      <c r="G5" s="20" t="s">
         <v>57</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="21">
         <v>135723</v>
       </c>
-      <c r="I5" s="21"/>
+      <c r="I5" s="20"/>
       <c r="J5" s="2">
         <v>2</v>
       </c>
-      <c r="L5" s="28" t="s">
+      <c r="L5" s="27" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="29">
+      <c r="M5" s="28">
         <v>195095</v>
       </c>
-      <c r="N5" s="28"/>
-      <c r="O5" s="30">
+      <c r="N5" s="27"/>
+      <c r="O5" s="29">
         <v>3</v>
       </c>
     </row>
     <row r="6" spans="2:15">
-      <c r="G6" s="21" t="s">
+      <c r="G6" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="H6" s="22">
+      <c r="H6" s="21">
         <v>73378</v>
       </c>
       <c r="I6" s="2" t="s">
@@ -2717,22 +2843,22 @@
       <c r="J6" s="2">
         <v>3</v>
       </c>
-      <c r="L6" s="21" t="s">
+      <c r="L6" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="M6" s="22">
+      <c r="M6" s="21">
         <v>234338</v>
       </c>
-      <c r="N6" s="21"/>
+      <c r="N6" s="20"/>
       <c r="O6" s="2">
         <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:15">
-      <c r="G7" s="21" t="s">
+      <c r="G7" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="H7" s="22">
+      <c r="H7" s="21">
         <v>138083</v>
       </c>
       <c r="I7" s="2" t="s">
@@ -2743,22 +2869,22 @@
       </c>
     </row>
     <row r="8" spans="2:15">
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="22">
+      <c r="H8" s="21">
         <v>64817</v>
       </c>
-      <c r="I8" s="21"/>
+      <c r="I8" s="20"/>
       <c r="J8" s="2">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:15">
-      <c r="G9" s="21" t="s">
+      <c r="G9" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="H9" s="22">
+      <c r="H9" s="21">
         <v>141342</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -2769,10 +2895,10 @@
       </c>
     </row>
     <row r="10" spans="2:15">
-      <c r="G10" s="21" t="s">
+      <c r="G10" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="H10" s="22">
+      <c r="H10" s="21">
         <v>50353</v>
       </c>
       <c r="I10" s="2" t="s">
@@ -2783,22 +2909,22 @@
       </c>
     </row>
     <row r="11" spans="2:15">
-      <c r="G11" s="21" t="s">
+      <c r="G11" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="H11" s="22">
+      <c r="H11" s="21">
         <v>118334</v>
       </c>
-      <c r="I11" s="21"/>
+      <c r="I11" s="20"/>
       <c r="J11" s="2">
         <v>8</v>
       </c>
     </row>
     <row r="12" spans="2:15">
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="H12" s="22">
+      <c r="H12" s="21">
         <v>104787</v>
       </c>
       <c r="I12" s="2" t="s">
@@ -2829,5 +2955,14 @@
     <hyperlink ref="G3" r:id="rId16" display="르유 호텔 알로나 팡라오 (LEUX HOTEL Alona Panglao)" xr:uid="{640F3647-02CB-4AF0-B744-46E1D857ED80}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Internal</oddFooter>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{7e753c2c-bb14-4786-921b-97c6a6fc424f}" enabled="1" method="Standard" siteId="{3bd97919-57c3-48d3-9e9a-8e4c01614a8f}" contentBits="2" removed="0"/>
+</clbl:labelList>
 </file>
--- a/travel/보홀/2026_보홀.xlsx
+++ b/travel/보홀/2026_보홀.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\git\csw\travel\보홀\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\보홀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65BFC745-BEFE-45BE-9F64-19ACB1F67A39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2A8AF5-22F8-4CD6-BC22-13E86503313B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
     <sheet name="예산" sheetId="4" r:id="rId2"/>
-    <sheet name="예약" sheetId="3" r:id="rId3"/>
+    <sheet name="예약" sheetId="6" r:id="rId3"/>
     <sheet name="숙소후보" sheetId="5" r:id="rId4"/>
   </sheets>
   <definedNames>
@@ -37,12 +37,15 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="106">
   <si>
     <t>토</t>
   </si>
@@ -433,27 +436,73 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>안경원숭이</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>한국 투어 (한바다 호핑)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>로복강 투어 (점심)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>육상 현지 투어 (반나절)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>한바다 투어</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>환율</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[숙박편]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[한바다호핑]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>예약비번 : h1117</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[항공편] - 세부퍼시픽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2. 비 그랜드 리조트 보홀 - 아고다</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1. 스텔라 팡라오 - 공식 홈페이지</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[유진 eSIM] - 클룩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[세원 eSIM] - 클룩</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[KTX] - 코레일톡(각자)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[공항철도] - 클룩 유진</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[공항버스] - 티머니고 세원</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>한바다 호핑
+리조트 픽업 (07:30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>기사 : Chris silagan
+리조트 픽업 (09:00)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>호핑투어 종료 (12:30)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -618,7 +667,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="26">
     <border>
       <left/>
       <right/>
@@ -866,6 +915,81 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -878,7 +1002,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1011,6 +1135,9 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1020,7 +1147,40 @@
     <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1047,22 +1207,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>167</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>323849</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>192157</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="그림 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DBE7955A-3A32-BC9C-57FA-66D98F7F13B6}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C369861-40FD-4001-9797-674FA0FAB99A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1078,8 +1238,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="685801" y="209551"/>
-          <a:ext cx="4800600" cy="5238916"/>
+          <a:off x="695325" y="647701"/>
+          <a:ext cx="4190999" cy="4573656"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1091,22 +1251,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>657226</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>209201</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>175045</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>390526</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>98774</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
+        <xdr:cNvPr id="3" name="그림 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{89D506C3-5F74-A2EC-E26B-93BE54FDC9F2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1BF3B3A-6305-440B-A0FE-EDA4007F35D4}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1122,8 +1282,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8915400" y="209550"/>
-          <a:ext cx="5953125" cy="5204245"/>
+          <a:off x="12811126" y="628301"/>
+          <a:ext cx="4152900" cy="3661473"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1134,23 +1294,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>419100</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>209549</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>95250</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>127094</xdr:rowOff>
+      <xdr:rowOff>27388</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="그림 4">
+        <xdr:cNvPr id="4" name="그림 3">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E85EEF0E-9642-CF57-8163-295938B5A1EA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD77FCB6-771B-48FB-AF7F-40A8165D5609}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1166,8 +1326,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14820900" y="209549"/>
-          <a:ext cx="5848350" cy="5156295"/>
+          <a:off x="17945100" y="619125"/>
+          <a:ext cx="5429250" cy="4647013"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1178,23 +1338,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>156842</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>106442</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="그림 5">
+        <xdr:cNvPr id="5" name="그림 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D81A491A-47D1-1479-13F5-A8E1FE6E8F34}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4E66DD8D-8AD0-4C44-842B-592EF2AB3AA8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1210,8 +1370,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="733425" y="5676900"/>
-          <a:ext cx="7505700" cy="6424292"/>
+          <a:off x="676275" y="9877425"/>
+          <a:ext cx="5343525" cy="3849767"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1222,23 +1382,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>2548</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>87392</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>400051</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>73057</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="그림 6">
+        <xdr:cNvPr id="6" name="그림 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6BA77F46-14C4-46A8-D1D5-E06DC957F75A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7CA6C1A9-91A0-48C0-A0E8-659791E00701}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1254,8 +1414,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8886825" y="5667375"/>
-          <a:ext cx="5343525" cy="3849767"/>
+          <a:off x="695326" y="5869948"/>
+          <a:ext cx="4267200" cy="2585109"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1266,23 +1426,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>447674</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>2451</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>592471</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>39265</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>714374</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>112799</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="그림 8">
+        <xdr:cNvPr id="7" name="그림 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{130F92DF-C149-7FB1-08BA-F9871CB03F02}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{99C760B8-7592-4945-8F6B-41A5D448FED1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1298,8 +1458,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14849474" y="5660301"/>
-          <a:ext cx="9745997" cy="5904214"/>
+          <a:off x="4914900" y="647701"/>
+          <a:ext cx="2419349" cy="4703848"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1310,23 +1470,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>19051</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>647701</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>651219</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>200025</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>586761</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>25452</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="그림 2">
+        <xdr:cNvPr id="8" name="그림 7">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2D49E2A-9F9D-8689-D537-2546A613A095}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02B88A0E-3FE0-4C1F-8FB5-C15063A0B12B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1342,8 +1502,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5505451" y="209550"/>
-          <a:ext cx="2689568" cy="5229225"/>
+          <a:off x="6315076" y="9886950"/>
+          <a:ext cx="2596535" cy="5645202"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1354,23 +1514,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>676276</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>270971</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>529611</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>139752</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>660668</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="그림 7">
+        <xdr:cNvPr id="9" name="그림 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{943356FA-9075-CD5E-7441-A281F14538DC}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9444E222-E06C-4211-BA13-11FFFCCE2D11}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1386,8 +1546,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8905876" y="9791700"/>
-          <a:ext cx="2596535" cy="5645202"/>
+          <a:off x="9176846" y="9896475"/>
+          <a:ext cx="2580447" cy="5610225"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1398,23 +1558,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>575771</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>28576</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>413018</xdr:colOff>
-      <xdr:row>73</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>130013</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="10" name="그림 9">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0661B66B-8BA8-3856-3350-3FCF1043B758}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1D21F5B-6CD4-4B6E-8863-D4E2B8A9C683}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1430,8 +1590,184 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="11548571" y="9801225"/>
-          <a:ext cx="2580447" cy="5610225"/>
+          <a:off x="8639176" y="657226"/>
+          <a:ext cx="4190999" cy="3663787"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>657225</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>219075</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>57709</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{212E2374-6E4E-4B8B-B02E-966407E829B0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9248775" y="5867401"/>
+          <a:ext cx="6858000" cy="2991408"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>200025</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>2451</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="그림 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{05963780-A59E-4D95-BAA1-1096A6BAAF9F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16078200" y="5857875"/>
+          <a:ext cx="5438775" cy="3155226"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>19051</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1876426</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>40723</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98EB20DC-E89D-0571-F2ED-6E9EB602C99F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4991101" y="5886451"/>
+          <a:ext cx="3238500" cy="2745822"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>25</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>466724</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>116556</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="그림 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C8A257A-A728-1503-3869-BDF5FD31A58E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21574125" y="6057900"/>
+          <a:ext cx="3695699" cy="6631656"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1846,9 +2182,9 @@
       <c r="C4" s="6"/>
       <c r="D4" s="5"/>
       <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="52"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="41" t="s">
@@ -1862,9 +2198,9 @@
       <c r="C5" s="6"/>
       <c r="D5" s="5"/>
       <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
+      <c r="F5" s="43"/>
       <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
+      <c r="H5" s="52"/>
       <c r="I5" s="42"/>
       <c r="J5" s="42"/>
       <c r="K5" s="5"/>
@@ -1878,9 +2214,9 @@
         <v>9.375E-2</v>
       </c>
       <c r="E6" s="42"/>
-      <c r="F6" s="42"/>
+      <c r="F6" s="43"/>
       <c r="G6" s="42"/>
-      <c r="H6" s="42"/>
+      <c r="H6" s="52"/>
       <c r="I6" s="42"/>
       <c r="J6" s="42"/>
       <c r="K6" s="5"/>
@@ -1894,9 +2230,9 @@
         <v>16</v>
       </c>
       <c r="E7" s="42"/>
-      <c r="F7" s="42"/>
+      <c r="F7" s="43"/>
       <c r="G7" s="42"/>
-      <c r="H7" s="42"/>
+      <c r="H7" s="52"/>
       <c r="I7" s="42"/>
       <c r="J7" s="42"/>
       <c r="K7" s="5"/>
@@ -1908,9 +2244,9 @@
       <c r="C8" s="6"/>
       <c r="D8" s="5"/>
       <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
+      <c r="H8" s="52"/>
       <c r="I8" s="42"/>
       <c r="J8" s="42"/>
       <c r="K8" s="5"/>
@@ -1924,9 +2260,9 @@
         <v>0.2361111111111111</v>
       </c>
       <c r="E9" s="42"/>
-      <c r="F9" s="42"/>
+      <c r="F9" s="43"/>
       <c r="G9" s="42"/>
-      <c r="H9" s="42"/>
+      <c r="H9" s="52"/>
       <c r="I9" s="42"/>
       <c r="J9" s="42"/>
       <c r="K9" s="41" t="s">
@@ -1942,9 +2278,9 @@
         <v>15</v>
       </c>
       <c r="E10" s="42"/>
-      <c r="F10" s="42"/>
+      <c r="F10" s="43"/>
       <c r="G10" s="42"/>
-      <c r="H10" s="42"/>
+      <c r="H10" s="52"/>
       <c r="I10" s="42"/>
       <c r="J10" s="43"/>
       <c r="K10" s="5" t="s">
@@ -1958,9 +2294,11 @@
       <c r="C11" s="6"/>
       <c r="D11" s="5"/>
       <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
+      <c r="F11" s="43"/>
+      <c r="G11" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="52"/>
       <c r="I11" s="42"/>
       <c r="J11" s="42"/>
       <c r="K11" s="40" t="s">
@@ -1974,16 +2312,16 @@
       <c r="C12" s="6"/>
       <c r="D12" s="5"/>
       <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
+      <c r="F12" s="43"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="52"/>
       <c r="I12" s="42"/>
       <c r="J12" s="42"/>
       <c r="K12" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" ht="33">
       <c r="B13" s="9">
         <v>0.375</v>
       </c>
@@ -1994,13 +2332,11 @@
       <c r="E13" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="3"/>
+      <c r="F13" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="G13" s="57"/>
+      <c r="H13" s="54"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="5"/>
@@ -2014,11 +2350,9 @@
         <v>15</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="F14" s="49"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="54"/>
       <c r="I14" s="3"/>
       <c r="J14" s="3"/>
       <c r="K14" s="5"/>
@@ -2032,11 +2366,11 @@
         <v>0.47222222222222221</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
+      <c r="F15" s="49" t="s">
+        <v>88</v>
+      </c>
+      <c r="G15" s="58"/>
+      <c r="H15" s="54"/>
       <c r="I15" s="3"/>
       <c r="J15" s="3"/>
       <c r="K15" s="5"/>
@@ -2050,11 +2384,13 @@
         <v>14</v>
       </c>
       <c r="E16" s="3"/>
-      <c r="F16" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3" t="s">
+      <c r="F16" s="49" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="H16" s="54" t="s">
         <v>70</v>
       </c>
       <c r="I16" s="3"/>
@@ -2063,16 +2399,18 @@
       </c>
       <c r="K16" s="5"/>
     </row>
-    <row r="17" spans="2:11">
+    <row r="17" spans="2:11" ht="17.25" thickBot="1">
       <c r="B17" s="9">
         <v>0.54166666666666696</v>
       </c>
       <c r="C17" s="6"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
+      <c r="F17" s="50" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="54"/>
+      <c r="H17" s="54"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3"/>
       <c r="K17" s="5"/>
@@ -2086,9 +2424,9 @@
         <v>69</v>
       </c>
       <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
+      <c r="F18" s="53"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="H18" s="54"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
       <c r="K18" s="5"/>
@@ -2100,9 +2438,9 @@
       <c r="C19" s="6"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
+      <c r="F19" s="53"/>
       <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
+      <c r="H19" s="54" t="s">
         <v>71</v>
       </c>
       <c r="I19" s="3"/>
@@ -2116,9 +2454,9 @@
       <c r="C20" s="6"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
+      <c r="F20" s="53"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="H20" s="54"/>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="5"/>
@@ -2130,9 +2468,9 @@
       <c r="C21" s="6"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
+      <c r="F21" s="53"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
+      <c r="H21" s="54"/>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="5"/>
@@ -2144,9 +2482,9 @@
       <c r="C22" s="6"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
+      <c r="F22" s="53"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="H22" s="54"/>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="5"/>
@@ -2158,9 +2496,9 @@
       <c r="C23" s="6"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="F23" s="53"/>
       <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
+      <c r="H23" s="54"/>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="5"/>
@@ -2172,9 +2510,9 @@
       <c r="C24" s="6"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
+      <c r="F24" s="53"/>
       <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="H24" s="54"/>
       <c r="J24" s="11">
         <v>0.85069444444444442</v>
       </c>
@@ -2189,9 +2527,9 @@
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
+      <c r="F25" s="53"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
+      <c r="H25" s="54"/>
       <c r="I25" s="3"/>
       <c r="J25" s="12" t="s">
         <v>14</v>
@@ -2207,9 +2545,9 @@
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
+      <c r="F26" s="53"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="H26" s="54"/>
       <c r="I26" s="3"/>
       <c r="J26" s="13">
         <v>0.92013888888888884</v>
@@ -2225,9 +2563,9 @@
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
+      <c r="F27" s="53"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="54"/>
       <c r="I27" s="3"/>
       <c r="J27" s="24" t="s">
         <v>15</v>
@@ -2239,17 +2577,17 @@
         <v>1</v>
       </c>
       <c r="C28" s="22"/>
-      <c r="D28" s="44" t="s">
+      <c r="D28" s="45" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="45"/>
-      <c r="F28" s="45"/>
-      <c r="G28" s="45"/>
+      <c r="E28" s="46"/>
+      <c r="F28" s="46"/>
+      <c r="G28" s="55"/>
       <c r="H28" s="26"/>
-      <c r="I28" s="45" t="s">
+      <c r="I28" s="46" t="s">
         <v>68</v>
       </c>
-      <c r="J28" s="46"/>
+      <c r="J28" s="47"/>
       <c r="K28" s="23"/>
     </row>
     <row r="31" spans="2:11">
@@ -2383,16 +2721,16 @@
       <c r="F2" s="30"/>
     </row>
     <row r="3" spans="2:6">
-      <c r="B3" s="47" t="s">
-        <v>94</v>
-      </c>
-      <c r="C3" s="47">
+      <c r="B3" s="44" t="s">
+        <v>91</v>
+      </c>
+      <c r="C3" s="44">
         <v>1</v>
       </c>
-      <c r="D3" s="47">
+      <c r="D3" s="44">
         <v>1470.5</v>
       </c>
-      <c r="E3" s="47">
+      <c r="E3" s="44">
         <v>23.84</v>
       </c>
       <c r="F3" s="30"/>
@@ -2487,7 +2825,7 @@
     </row>
     <row r="12" spans="2:6">
       <c r="B12" s="31" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C12" s="32">
         <v>40000</v>
@@ -2669,15 +3007,60 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4CB3F24-E440-4CFB-AA49-9CEA408CE6AD}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AFF2DE67-503A-4D9F-AB80-FE99DB56590E}">
+  <dimension ref="B3:U47"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.25" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="8.875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:21">
+      <c r="B3" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="J3" s="51" t="s">
+        <v>92</v>
+      </c>
+      <c r="K3" s="51" t="s">
+        <v>97</v>
+      </c>
+      <c r="U3" s="51" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
+      <c r="B28" s="51" t="s">
+        <v>99</v>
+      </c>
+      <c r="G28" s="51" t="s">
+        <v>98</v>
+      </c>
+      <c r="K28" s="51" t="s">
+        <v>93</v>
+      </c>
+      <c r="L28" s="51" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="2:15">
+      <c r="B47" s="51" t="s">
+        <v>101</v>
+      </c>
+      <c r="I47" s="51" t="s">
+        <v>102</v>
+      </c>
+      <c r="O47" s="51" t="s">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter>
-    <oddFooter>&amp;C_x000D_&amp;1#&amp;"Aptos"&amp;8&amp;K000000 Internal</oddFooter>
-  </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
 </file>

--- a/travel/보홀/2026_보홀.xlsx
+++ b/travel/보홀/2026_보홀.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git\csw\travel\보홀\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2A8AF5-22F8-4CD6-BC22-13E86503313B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{168C2D8C-0C26-42B6-9724-07454632C862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7A13A56E-5A3D-46D4-B5B2-6E63EA029A48}"/>
   </bookViews>
   <sheets>
     <sheet name="일정" sheetId="1" r:id="rId1"/>
@@ -20,8 +20,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숙소후보!$B$2:$R$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">일정!$D$13:$H$19</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="166">
   <si>
     <t>토</t>
   </si>
@@ -338,10 +339,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>스텔라 팡라오</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>숙소(스텔라팡라오)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -424,10 +421,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>현지인 투어</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>인천공항-광명 공항버스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -503,6 +496,193 @@
   </si>
   <si>
     <t>호핑투어 종료 (12:30)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>공항 커피</t>
+  </si>
+  <si>
+    <t>공항 툭툭 픽업</t>
+  </si>
+  <si>
+    <t>네일</t>
+  </si>
+  <si>
+    <t>풋</t>
+  </si>
+  <si>
+    <t>졸리비</t>
+  </si>
+  <si>
+    <t>육상투어</t>
+  </si>
+  <si>
+    <t>할로망고</t>
+  </si>
+  <si>
+    <t>게리스 그릴</t>
+  </si>
+  <si>
+    <t>발리카삭 현지투어</t>
+  </si>
+  <si>
+    <t>코코넛 주스</t>
+  </si>
+  <si>
+    <t>나팔링 입장료</t>
+  </si>
+  <si>
+    <t>나팔링 고프로</t>
+  </si>
+  <si>
+    <t>나팔링 가이드</t>
+  </si>
+  <si>
+    <t>나팔링 툭툭</t>
+  </si>
+  <si>
+    <t>갈릭 레몬</t>
+  </si>
+  <si>
+    <t>불쇼</t>
+  </si>
+  <si>
+    <t>불쇼 맥주</t>
+  </si>
+  <si>
+    <t>초콜릿힐</t>
+  </si>
+  <si>
+    <t>로복강 음료수</t>
+  </si>
+  <si>
+    <t>로복강 투어</t>
+  </si>
+  <si>
+    <t>안경숭이 기념품</t>
+  </si>
+  <si>
+    <t>안경원숭이 투어</t>
+  </si>
+  <si>
+    <t>픽업 가이드</t>
+  </si>
+  <si>
+    <t>픽업 팁</t>
+  </si>
+  <si>
+    <t>망고 코코넛 빙수</t>
+  </si>
+  <si>
+    <t>해피밀</t>
+  </si>
+  <si>
+    <t>세븐일레븐</t>
+  </si>
+  <si>
+    <t>마사지</t>
+  </si>
+  <si>
+    <t>마사지 팁</t>
+  </si>
+  <si>
+    <t>BBC 데이유즈</t>
+  </si>
+  <si>
+    <t>bbc 툭툭</t>
+  </si>
+  <si>
+    <t>bbc 입장료</t>
+  </si>
+  <si>
+    <t>아툴라스 마켓</t>
+  </si>
+  <si>
+    <t>복귀 툭툭</t>
+  </si>
+  <si>
+    <t>밤부</t>
+  </si>
+  <si>
+    <t>몽키트리</t>
+  </si>
+  <si>
+    <t>아툴라스 팡라오 슈퍼마켓 탐방</t>
+  </si>
+  <si>
+    <t>밤부 저녁</t>
+  </si>
+  <si>
+    <t>몽키트리 탐방</t>
+  </si>
+  <si>
+    <t>돌조비치 픽업(08:30)</t>
+  </si>
+  <si>
+    <t>발리카삭 현지인 투어</t>
+  </si>
+  <si>
+    <t>알로나 비치</t>
+  </si>
+  <si>
+    <t>jnp</t>
+  </si>
+  <si>
+    <t>jnp 픽업</t>
+  </si>
+  <si>
+    <t>비그랜드 픽업</t>
+  </si>
+  <si>
+    <t>룸 팁</t>
+  </si>
+  <si>
+    <t>소품샵</t>
+  </si>
+  <si>
+    <t>우베코</t>
+  </si>
+  <si>
+    <t>편의점</t>
+  </si>
+  <si>
+    <t>비그랜드 피자</t>
+  </si>
+  <si>
+    <t>빠우</t>
+  </si>
+  <si>
+    <t>라벨라 마사지</t>
+  </si>
+  <si>
+    <t>코코넛 과육 까사바</t>
+  </si>
+  <si>
+    <t>스톤 마사지</t>
+  </si>
+  <si>
+    <t>돌조비치 픽업(10:00)</t>
+  </si>
+  <si>
+    <t>브릿지 카페 - 피자</t>
+  </si>
+  <si>
+    <t>과포 레스토랑</t>
+  </si>
+  <si>
+    <t>나팔링 투어</t>
+  </si>
+  <si>
+    <t>더타이보홀 마사지</t>
+  </si>
+  <si>
+    <t>와플</t>
+  </si>
+  <si>
+    <t>편의점 물</t>
+  </si>
+  <si>
+    <t>인천공항-세종 공항버스</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -510,12 +690,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
-    <numFmt numFmtId="177" formatCode="#,##0_);[Red]\(#,##0\)"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -598,6 +777,24 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <strike/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -667,7 +864,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="33">
     <border>
       <left/>
       <right/>
@@ -990,6 +1187,89 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF505050"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF505050"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF505050"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF505050"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1002,7 +1282,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1066,7 +1346,7 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="0" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1087,7 +1367,7 @@
     <xf numFmtId="0" fontId="10" fillId="10" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="38" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1138,18 +1418,6 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="19" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1168,19 +1436,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="27" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="29" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="7" borderId="30" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="31" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="32" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="25" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2184,11 +2491,11 @@
       <c r="E4" s="42"/>
       <c r="F4" s="43"/>
       <c r="G4" s="34"/>
-      <c r="H4" s="52"/>
+      <c r="H4" s="48"/>
       <c r="I4" s="42"/>
       <c r="J4" s="42"/>
       <c r="K4" s="41" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:13" ht="17.25" thickBot="1">
@@ -2200,7 +2507,7 @@
       <c r="E5" s="42"/>
       <c r="F5" s="43"/>
       <c r="G5" s="42"/>
-      <c r="H5" s="52"/>
+      <c r="H5" s="48"/>
       <c r="I5" s="42"/>
       <c r="J5" s="42"/>
       <c r="K5" s="5"/>
@@ -2216,7 +2523,7 @@
       <c r="E6" s="42"/>
       <c r="F6" s="43"/>
       <c r="G6" s="42"/>
-      <c r="H6" s="52"/>
+      <c r="H6" s="48"/>
       <c r="I6" s="42"/>
       <c r="J6" s="42"/>
       <c r="K6" s="5"/>
@@ -2232,7 +2539,7 @@
       <c r="E7" s="42"/>
       <c r="F7" s="43"/>
       <c r="G7" s="42"/>
-      <c r="H7" s="52"/>
+      <c r="H7" s="48"/>
       <c r="I7" s="42"/>
       <c r="J7" s="42"/>
       <c r="K7" s="5"/>
@@ -2246,7 +2553,7 @@
       <c r="E8" s="42"/>
       <c r="F8" s="43"/>
       <c r="G8" s="42"/>
-      <c r="H8" s="52"/>
+      <c r="H8" s="48"/>
       <c r="I8" s="42"/>
       <c r="J8" s="42"/>
       <c r="K8" s="5"/>
@@ -2262,11 +2569,11 @@
       <c r="E9" s="42"/>
       <c r="F9" s="43"/>
       <c r="G9" s="42"/>
-      <c r="H9" s="52"/>
+      <c r="H9" s="48"/>
       <c r="I9" s="42"/>
       <c r="J9" s="42"/>
       <c r="K9" s="41" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="17.25" thickBot="1">
@@ -2280,14 +2587,14 @@
       <c r="E10" s="42"/>
       <c r="F10" s="43"/>
       <c r="G10" s="42"/>
-      <c r="H10" s="52"/>
+      <c r="H10" s="48"/>
       <c r="I10" s="42"/>
       <c r="J10" s="43"/>
       <c r="K10" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" ht="33">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="33.75" thickBot="1">
       <c r="B11" s="9">
         <v>0.29166666666666702</v>
       </c>
@@ -2295,14 +2602,14 @@
       <c r="D11" s="5"/>
       <c r="E11" s="42"/>
       <c r="F11" s="43"/>
-      <c r="G11" s="48" t="s">
-        <v>103</v>
-      </c>
-      <c r="H11" s="52"/>
+      <c r="G11" s="53" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="48"/>
       <c r="I11" s="42"/>
       <c r="J11" s="42"/>
       <c r="K11" s="40" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="17.25" thickBot="1">
@@ -2313,35 +2620,41 @@
       <c r="D12" s="5"/>
       <c r="E12" s="42"/>
       <c r="F12" s="43"/>
-      <c r="G12" s="49"/>
-      <c r="H12" s="52"/>
+      <c r="G12" s="56"/>
+      <c r="H12" s="54" t="s">
+        <v>143</v>
+      </c>
       <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
+      <c r="J12" s="54" t="s">
+        <v>143</v>
+      </c>
       <c r="K12" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" ht="33">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" ht="33.75" thickBot="1">
       <c r="B13" s="9">
         <v>0.375</v>
       </c>
       <c r="C13" s="6"/>
-      <c r="D13" s="11">
+      <c r="D13" s="60">
         <v>0.39930555555555558</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="F13" s="48" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" s="57"/>
-      <c r="H13" s="54"/>
+      <c r="E13" s="59" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="61" t="s">
+        <v>102</v>
+      </c>
+      <c r="G13" s="56" t="s">
+        <v>133</v>
+      </c>
+      <c r="H13" s="55"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="3"/>
+      <c r="J13" s="55"/>
       <c r="K13" s="5"/>
     </row>
-    <row r="14" spans="1:13">
+    <row r="14" spans="1:13" ht="17.25" thickBot="1">
       <c r="B14" s="9">
         <v>0.41666666666666702</v>
       </c>
@@ -2350,11 +2663,13 @@
         <v>15</v>
       </c>
       <c r="E14" s="3"/>
-      <c r="F14" s="49"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="54"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
+      <c r="F14" s="45"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="62"/>
+      <c r="I14" s="59" t="s">
+        <v>158</v>
+      </c>
+      <c r="J14" s="62"/>
       <c r="K14" s="5"/>
     </row>
     <row r="15" spans="1:13">
@@ -2366,12 +2681,16 @@
         <v>0.47222222222222221</v>
       </c>
       <c r="E15" s="3"/>
-      <c r="F15" s="49" t="s">
-        <v>88</v>
-      </c>
-      <c r="G15" s="58"/>
-      <c r="H15" s="54"/>
-      <c r="I15" s="3"/>
+      <c r="F15" s="45" t="s">
+        <v>86</v>
+      </c>
+      <c r="G15" s="52"/>
+      <c r="H15" s="50" t="s">
+        <v>156</v>
+      </c>
+      <c r="I15" s="50" t="s">
+        <v>156</v>
+      </c>
       <c r="J15" s="3"/>
       <c r="K15" s="5"/>
     </row>
@@ -2383,19 +2702,21 @@
       <c r="D16" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="49" t="s">
+      <c r="E16" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="F16" s="45" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="59" t="s">
-        <v>105</v>
-      </c>
-      <c r="H16" s="54" t="s">
-        <v>70</v>
-      </c>
-      <c r="I16" s="3"/>
+      <c r="G16" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>69</v>
+      </c>
+      <c r="I16" s="50"/>
       <c r="J16" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="K16" s="5"/>
     </row>
@@ -2406,13 +2727,15 @@
       <c r="C17" s="6"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-      <c r="F17" s="50" t="s">
-        <v>89</v>
-      </c>
-      <c r="G17" s="54"/>
-      <c r="H17" s="54"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3"/>
+      <c r="F17" s="46" t="s">
+        <v>87</v>
+      </c>
+      <c r="G17" s="50"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
+      <c r="J17" s="3" t="s">
+        <v>160</v>
+      </c>
       <c r="K17" s="5"/>
     </row>
     <row r="18" spans="2:11">
@@ -2421,14 +2744,20 @@
       </c>
       <c r="C18" s="6"/>
       <c r="D18" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="53"/>
+        <v>68</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F18" s="49"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50" t="s">
+        <v>159</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>162</v>
+      </c>
       <c r="K18" s="5"/>
     </row>
     <row r="19" spans="2:11">
@@ -2438,12 +2767,16 @@
       <c r="C19" s="6"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="54" t="s">
-        <v>71</v>
-      </c>
-      <c r="I19" s="3"/>
+      <c r="F19" s="49" t="s">
+        <v>129</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="I19" s="50"/>
       <c r="J19" s="3"/>
       <c r="K19" s="5"/>
     </row>
@@ -2454,10 +2787,10 @@
       <c r="C20" s="6"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-      <c r="F20" s="53"/>
+      <c r="F20" s="49"/>
       <c r="G20" s="3"/>
-      <c r="H20" s="54"/>
-      <c r="I20" s="3"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
       <c r="J20" s="3"/>
       <c r="K20" s="5"/>
     </row>
@@ -2468,10 +2801,10 @@
       <c r="C21" s="6"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-      <c r="F21" s="53"/>
+      <c r="F21" s="49"/>
       <c r="G21" s="3"/>
-      <c r="H21" s="54"/>
-      <c r="I21" s="3"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="50"/>
       <c r="J21" s="3"/>
       <c r="K21" s="5"/>
     </row>
@@ -2480,12 +2813,20 @@
         <v>0.75</v>
       </c>
       <c r="C22" s="6"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="53"/>
+      <c r="D22" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="F22" s="49"/>
       <c r="G22" s="3"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="3"/>
+      <c r="H22" s="50" t="s">
+        <v>151</v>
+      </c>
+      <c r="I22" s="50" t="s">
+        <v>154</v>
+      </c>
       <c r="J22" s="3"/>
       <c r="K22" s="5"/>
     </row>
@@ -2496,10 +2837,12 @@
       <c r="C23" s="6"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-      <c r="F23" s="53"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="54"/>
-      <c r="I23" s="3"/>
+      <c r="F23" s="49"/>
+      <c r="G23" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" s="50"/>
+      <c r="I23" s="50"/>
       <c r="J23" s="3"/>
       <c r="K23" s="5"/>
     </row>
@@ -2510,9 +2853,16 @@
       <c r="C24" s="6"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-      <c r="F24" s="53"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="54"/>
+      <c r="F24" s="49" t="s">
+        <v>157</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="H24" s="50"/>
+      <c r="I24" s="50" t="s">
+        <v>155</v>
+      </c>
       <c r="J24" s="11">
         <v>0.85069444444444442</v>
       </c>
@@ -2523,13 +2873,15 @@
         <v>0.875</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="53"/>
+      <c r="E25" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="49"/>
       <c r="G25" s="3"/>
-      <c r="H25" s="54"/>
+      <c r="H25" s="50"/>
       <c r="I25" s="3"/>
       <c r="J25" s="12" t="s">
         <v>14</v>
@@ -2541,13 +2893,13 @@
         <v>0.91666666666666696</v>
       </c>
       <c r="C26" s="39" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-      <c r="F26" s="53"/>
+      <c r="F26" s="49"/>
       <c r="G26" s="3"/>
-      <c r="H26" s="54"/>
+      <c r="H26" s="50"/>
       <c r="I26" s="3"/>
       <c r="J26" s="13">
         <v>0.92013888888888884</v>
@@ -2559,13 +2911,13 @@
         <v>0.95833333333333304</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="53"/>
-      <c r="G27" s="56"/>
-      <c r="H27" s="54"/>
+      <c r="F27" s="49"/>
+      <c r="G27" s="51"/>
+      <c r="H27" s="50"/>
       <c r="I27" s="3"/>
       <c r="J27" s="24" t="s">
         <v>15</v>
@@ -2577,17 +2929,17 @@
         <v>1</v>
       </c>
       <c r="C28" s="22"/>
-      <c r="D28" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="E28" s="46"/>
-      <c r="F28" s="46"/>
-      <c r="G28" s="55"/>
+      <c r="D28" s="63" t="s">
+        <v>64</v>
+      </c>
+      <c r="E28" s="64"/>
+      <c r="F28" s="64"/>
+      <c r="G28" s="65"/>
       <c r="H28" s="26"/>
-      <c r="I28" s="46" t="s">
-        <v>68</v>
-      </c>
-      <c r="J28" s="47"/>
+      <c r="I28" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="J28" s="66"/>
       <c r="K28" s="23"/>
     </row>
     <row r="31" spans="2:11">
@@ -2629,7 +2981,7 @@
     </row>
     <row r="36" spans="3:9">
       <c r="C36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
         <v>22</v>
@@ -2696,14 +3048,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37B29DE7-3267-4196-8A3E-54333E9A8DE2}">
-  <dimension ref="B2:F33"/>
+  <dimension ref="B2:F74"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="4.125" customWidth="1"/>
     <col min="2" max="2" width="22.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="7.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.75" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2722,7 +3074,7 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" s="44" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C3" s="44">
         <v>1</v>
@@ -2748,7 +3100,7 @@
     </row>
     <row r="5" spans="2:6">
       <c r="B5" s="31" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C5" s="32">
         <v>345632</v>
@@ -2759,7 +3111,7 @@
     </row>
     <row r="6" spans="2:6">
       <c r="B6" s="31" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C6" s="32">
         <v>348623</v>
@@ -2770,7 +3122,7 @@
     </row>
     <row r="7" spans="2:6">
       <c r="B7" s="31" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C7" s="32">
         <v>23000</v>
@@ -2780,30 +3132,26 @@
       <c r="F7" s="33"/>
     </row>
     <row r="8" spans="2:6">
-      <c r="B8" s="31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C8" s="32">
-        <v>37000</v>
-      </c>
+      <c r="B8" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="C8" s="32"/>
       <c r="D8" s="32"/>
       <c r="E8" s="32"/>
       <c r="F8" s="33"/>
     </row>
     <row r="9" spans="2:6">
-      <c r="B9" s="31" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="32">
-        <v>32200</v>
-      </c>
+      <c r="B9" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="32"/>
       <c r="D9" s="32"/>
       <c r="E9" s="32"/>
       <c r="F9" s="33"/>
     </row>
     <row r="10" spans="2:6">
       <c r="B10" s="31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C10" s="32">
         <v>9618</v>
@@ -2813,188 +3161,709 @@
       <c r="F10" s="33"/>
     </row>
     <row r="11" spans="2:6">
-      <c r="B11" s="31" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="32">
-        <v>32000</v>
-      </c>
+      <c r="B11" s="68" t="s">
+        <v>85</v>
+      </c>
+      <c r="C11" s="32"/>
       <c r="D11" s="32"/>
       <c r="E11" s="32"/>
       <c r="F11" s="33"/>
     </row>
     <row r="12" spans="2:6">
-      <c r="B12" s="31" t="s">
-        <v>90</v>
-      </c>
-      <c r="C12" s="32">
-        <v>40000</v>
-      </c>
+      <c r="B12" s="67" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="32"/>
       <c r="D12" s="32"/>
-      <c r="E12" s="32">
-        <v>6000</v>
-      </c>
+      <c r="E12" s="32"/>
       <c r="F12" s="33"/>
     </row>
     <row r="13" spans="2:6">
-      <c r="B13" s="31"/>
+      <c r="B13" s="31" t="s">
+        <v>104</v>
+      </c>
       <c r="C13" s="32"/>
       <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
+      <c r="E13" s="32">
+        <v>120</v>
+      </c>
       <c r="F13" s="33"/>
     </row>
     <row r="14" spans="2:6">
-      <c r="B14" s="31"/>
+      <c r="B14" s="31" t="s">
+        <v>105</v>
+      </c>
       <c r="C14" s="32"/>
       <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
+      <c r="E14" s="32">
+        <v>200</v>
+      </c>
       <c r="F14" s="33"/>
     </row>
     <row r="15" spans="2:6">
-      <c r="B15" s="31"/>
+      <c r="B15" s="31" t="s">
+        <v>106</v>
+      </c>
       <c r="C15" s="32"/>
       <c r="D15" s="32"/>
-      <c r="E15" s="32"/>
+      <c r="E15" s="32">
+        <v>2700</v>
+      </c>
       <c r="F15" s="33"/>
     </row>
     <row r="16" spans="2:6">
-      <c r="B16" s="31"/>
+      <c r="B16" s="31" t="s">
+        <v>107</v>
+      </c>
       <c r="C16" s="32"/>
       <c r="D16" s="32"/>
-      <c r="E16" s="32"/>
+      <c r="E16" s="32">
+        <v>1100</v>
+      </c>
       <c r="F16" s="33"/>
     </row>
     <row r="17" spans="2:6">
-      <c r="B17" s="31"/>
+      <c r="B17" s="31" t="s">
+        <v>108</v>
+      </c>
       <c r="C17" s="32"/>
       <c r="D17" s="32"/>
-      <c r="E17" s="32"/>
+      <c r="E17" s="32">
+        <v>412</v>
+      </c>
       <c r="F17" s="33"/>
     </row>
     <row r="18" spans="2:6">
-      <c r="B18" s="31"/>
+      <c r="B18" s="31" t="s">
+        <v>109</v>
+      </c>
       <c r="C18" s="32"/>
       <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
+      <c r="E18" s="32">
+        <v>2500</v>
+      </c>
       <c r="F18" s="33"/>
     </row>
     <row r="19" spans="2:6">
-      <c r="B19" s="31"/>
+      <c r="B19" s="31" t="s">
+        <v>110</v>
+      </c>
       <c r="C19" s="32"/>
       <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
+      <c r="E19" s="32">
+        <v>300</v>
+      </c>
       <c r="F19" s="33"/>
     </row>
     <row r="20" spans="2:6">
-      <c r="B20" s="31"/>
+      <c r="B20" s="31" t="s">
+        <v>111</v>
+      </c>
       <c r="C20" s="32"/>
       <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
+      <c r="E20" s="32">
+        <v>3025</v>
+      </c>
       <c r="F20" s="33"/>
     </row>
     <row r="21" spans="2:6">
-      <c r="B21" s="31"/>
+      <c r="B21" s="31" t="s">
+        <v>112</v>
+      </c>
       <c r="C21" s="32"/>
       <c r="D21" s="32"/>
-      <c r="E21" s="32"/>
+      <c r="E21" s="32">
+        <v>3300</v>
+      </c>
       <c r="F21" s="33"/>
     </row>
     <row r="22" spans="2:6">
-      <c r="B22" s="31"/>
+      <c r="B22" s="31" t="s">
+        <v>113</v>
+      </c>
       <c r="C22" s="32"/>
       <c r="D22" s="32"/>
-      <c r="E22" s="32"/>
+      <c r="E22" s="32">
+        <v>150</v>
+      </c>
       <c r="F22" s="33"/>
     </row>
     <row r="23" spans="2:6">
-      <c r="B23" s="31"/>
+      <c r="B23" s="31" t="s">
+        <v>116</v>
+      </c>
       <c r="C23" s="32"/>
       <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
+      <c r="E23" s="32">
+        <v>400</v>
+      </c>
       <c r="F23" s="33"/>
     </row>
     <row r="24" spans="2:6">
-      <c r="B24" s="31"/>
+      <c r="B24" s="31" t="s">
+        <v>114</v>
+      </c>
       <c r="C24" s="32"/>
       <c r="D24" s="32"/>
-      <c r="E24" s="32"/>
+      <c r="E24" s="32">
+        <v>200</v>
+      </c>
       <c r="F24" s="33"/>
     </row>
     <row r="25" spans="2:6">
-      <c r="B25" s="31"/>
+      <c r="B25" s="31" t="s">
+        <v>115</v>
+      </c>
       <c r="C25" s="32"/>
       <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
+      <c r="E25" s="32">
+        <v>500</v>
+      </c>
       <c r="F25" s="33"/>
     </row>
     <row r="26" spans="2:6">
-      <c r="B26" s="31"/>
+      <c r="B26" s="31" t="s">
+        <v>117</v>
+      </c>
       <c r="C26" s="32"/>
       <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
+      <c r="E26" s="32">
+        <v>400</v>
+      </c>
       <c r="F26" s="33"/>
     </row>
     <row r="27" spans="2:6">
-      <c r="B27" s="31"/>
+      <c r="B27" s="31" t="s">
+        <v>118</v>
+      </c>
       <c r="C27" s="32"/>
       <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
+      <c r="E27" s="32">
+        <v>1350</v>
+      </c>
       <c r="F27" s="33"/>
     </row>
     <row r="28" spans="2:6">
-      <c r="B28" s="31"/>
+      <c r="B28" s="31" t="s">
+        <v>119</v>
+      </c>
       <c r="C28" s="32"/>
       <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
+      <c r="E28" s="32">
+        <v>300</v>
+      </c>
       <c r="F28" s="33"/>
     </row>
     <row r="29" spans="2:6">
-      <c r="B29" s="31"/>
+      <c r="B29" s="31" t="s">
+        <v>120</v>
+      </c>
       <c r="C29" s="32"/>
       <c r="D29" s="32"/>
-      <c r="E29" s="32"/>
+      <c r="E29" s="32">
+        <v>250</v>
+      </c>
       <c r="F29" s="33"/>
     </row>
     <row r="30" spans="2:6">
-      <c r="B30" s="31"/>
+      <c r="B30" s="31" t="s">
+        <v>121</v>
+      </c>
       <c r="C30" s="32"/>
       <c r="D30" s="32"/>
-      <c r="E30" s="32"/>
+      <c r="E30" s="32">
+        <v>200</v>
+      </c>
       <c r="F30" s="33"/>
     </row>
     <row r="31" spans="2:6">
-      <c r="B31" s="31"/>
+      <c r="B31" s="31" t="s">
+        <v>125</v>
+      </c>
       <c r="C31" s="32"/>
       <c r="D31" s="32"/>
-      <c r="E31" s="32"/>
+      <c r="E31" s="32">
+        <v>360</v>
+      </c>
       <c r="F31" s="33"/>
     </row>
-    <row r="32" spans="2:6" ht="17.25" thickBot="1">
-      <c r="B32" s="34"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
+    <row r="32" spans="2:6">
+      <c r="B32" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C32" s="32"/>
+      <c r="D32" s="32"/>
+      <c r="E32" s="32">
+        <v>270</v>
+      </c>
       <c r="F32" s="33"/>
     </row>
-    <row r="33" spans="2:6" ht="17.25" thickBot="1">
-      <c r="B33" s="36" t="s">
+    <row r="33" spans="2:6">
+      <c r="B33" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="C33" s="32"/>
+      <c r="D33" s="32"/>
+      <c r="E33" s="32">
+        <v>2400</v>
+      </c>
+      <c r="F33" s="33"/>
+    </row>
+    <row r="34" spans="2:6">
+      <c r="B34" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C34" s="32"/>
+      <c r="D34" s="32"/>
+      <c r="E34" s="32">
+        <v>180</v>
+      </c>
+      <c r="F34" s="33"/>
+    </row>
+    <row r="35" spans="2:6">
+      <c r="B35" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="C35" s="32"/>
+      <c r="D35" s="32"/>
+      <c r="E35" s="32">
+        <v>2500</v>
+      </c>
+      <c r="F35" s="33"/>
+    </row>
+    <row r="36" spans="2:6">
+      <c r="B36" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C36" s="32"/>
+      <c r="D36" s="32"/>
+      <c r="E36" s="32">
+        <v>200</v>
+      </c>
+      <c r="F36" s="33"/>
+    </row>
+    <row r="37" spans="2:6">
+      <c r="B37" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C37" s="32"/>
+      <c r="D37" s="32"/>
+      <c r="E37" s="32">
+        <v>350</v>
+      </c>
+      <c r="F37" s="33"/>
+    </row>
+    <row r="38" spans="2:6">
+      <c r="B38" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32">
+        <v>99</v>
+      </c>
+      <c r="F38" s="33"/>
+    </row>
+    <row r="39" spans="2:6">
+      <c r="B39" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32">
+        <v>300</v>
+      </c>
+      <c r="F39" s="33"/>
+    </row>
+    <row r="40" spans="2:6">
+      <c r="B40" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C40" s="32"/>
+      <c r="D40" s="32"/>
+      <c r="E40" s="32">
+        <v>186.5</v>
+      </c>
+      <c r="F40" s="33"/>
+    </row>
+    <row r="41" spans="2:6">
+      <c r="B41" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32">
+        <v>3000</v>
+      </c>
+      <c r="F41" s="33"/>
+    </row>
+    <row r="42" spans="2:6">
+      <c r="B42" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C42" s="32"/>
+      <c r="D42" s="32"/>
+      <c r="E42" s="32">
+        <v>200</v>
+      </c>
+      <c r="F42" s="33"/>
+    </row>
+    <row r="43" spans="2:6">
+      <c r="B43" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C43" s="32"/>
+      <c r="D43" s="32"/>
+      <c r="E43" s="32">
+        <v>317</v>
+      </c>
+      <c r="F43" s="33"/>
+    </row>
+    <row r="44" spans="2:6">
+      <c r="B44" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C44" s="32"/>
+      <c r="D44" s="32"/>
+      <c r="E44" s="32">
+        <v>150</v>
+      </c>
+      <c r="F44" s="33"/>
+    </row>
+    <row r="45" spans="2:6">
+      <c r="B45" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C45" s="32"/>
+      <c r="D45" s="32"/>
+      <c r="E45" s="32">
+        <v>2400</v>
+      </c>
+      <c r="F45" s="33"/>
+    </row>
+    <row r="46" spans="2:6">
+      <c r="B46" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="32"/>
+      <c r="D46" s="32"/>
+      <c r="E46" s="32">
+        <v>2876.15</v>
+      </c>
+      <c r="F46" s="33"/>
+    </row>
+    <row r="47" spans="2:6">
+      <c r="B47" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C47" s="32"/>
+      <c r="D47" s="32"/>
+      <c r="E47" s="32">
+        <v>300</v>
+      </c>
+      <c r="F47" s="33"/>
+    </row>
+    <row r="48" spans="2:6">
+      <c r="B48" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="C48" s="32"/>
+      <c r="D48" s="32"/>
+      <c r="E48" s="32">
+        <v>1565</v>
+      </c>
+      <c r="F48" s="33"/>
+    </row>
+    <row r="49" spans="2:6">
+      <c r="B49" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="32"/>
+      <c r="D49" s="32"/>
+      <c r="E49" s="32">
+        <v>1050</v>
+      </c>
+      <c r="F49" s="33"/>
+    </row>
+    <row r="50" spans="2:6">
+      <c r="B50" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C50" s="32"/>
+      <c r="D50" s="32"/>
+      <c r="E50" s="32">
+        <v>1400</v>
+      </c>
+      <c r="F50" s="33"/>
+    </row>
+    <row r="51" spans="2:6">
+      <c r="B51" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="32"/>
+      <c r="D51" s="32"/>
+      <c r="E51" s="32">
+        <v>105</v>
+      </c>
+      <c r="F51" s="33"/>
+    </row>
+    <row r="52" spans="2:6">
+      <c r="B52" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C52" s="32"/>
+      <c r="D52" s="32"/>
+      <c r="E52" s="32">
+        <v>400</v>
+      </c>
+      <c r="F52" s="33"/>
+    </row>
+    <row r="53" spans="2:6">
+      <c r="B53" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C53" s="32"/>
+      <c r="D53" s="32"/>
+      <c r="E53" s="32">
+        <v>100</v>
+      </c>
+      <c r="F53" s="33"/>
+    </row>
+    <row r="54" spans="2:6">
+      <c r="B54" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="32"/>
+      <c r="D54" s="32"/>
+      <c r="E54" s="32">
+        <v>50</v>
+      </c>
+      <c r="F54" s="33"/>
+    </row>
+    <row r="55" spans="2:6">
+      <c r="B55" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="C55" s="32"/>
+      <c r="D55" s="32"/>
+      <c r="E55" s="32">
+        <v>200</v>
+      </c>
+      <c r="F55" s="33"/>
+    </row>
+    <row r="56" spans="2:6">
+      <c r="B56" s="31" t="s">
+        <v>151</v>
+      </c>
+      <c r="C56" s="32"/>
+      <c r="D56" s="32"/>
+      <c r="E56" s="32">
+        <v>1400</v>
+      </c>
+      <c r="F56" s="33"/>
+    </row>
+    <row r="57" spans="2:6">
+      <c r="B57" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C57" s="32"/>
+      <c r="D57" s="32"/>
+      <c r="E57" s="32">
+        <v>506.5</v>
+      </c>
+      <c r="F57" s="33"/>
+    </row>
+    <row r="58" spans="2:6">
+      <c r="B58" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C58" s="32"/>
+      <c r="D58" s="32"/>
+      <c r="E58" s="32">
+        <v>1400</v>
+      </c>
+      <c r="F58" s="33"/>
+    </row>
+    <row r="59" spans="2:6">
+      <c r="B59" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32">
+        <v>105</v>
+      </c>
+      <c r="F59" s="33"/>
+    </row>
+    <row r="60" spans="2:6">
+      <c r="B60" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60" s="32"/>
+      <c r="D60" s="32"/>
+      <c r="E60" s="32">
+        <v>400</v>
+      </c>
+      <c r="F60" s="33"/>
+    </row>
+    <row r="61" spans="2:6">
+      <c r="B61" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="C61" s="32"/>
+      <c r="D61" s="32"/>
+      <c r="E61" s="32">
+        <v>580</v>
+      </c>
+      <c r="F61" s="33"/>
+    </row>
+    <row r="62" spans="2:6">
+      <c r="B62" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="C62" s="32"/>
+      <c r="D62" s="32"/>
+      <c r="E62" s="32">
+        <v>1950</v>
+      </c>
+      <c r="F62" s="33"/>
+    </row>
+    <row r="63" spans="2:6">
+      <c r="B63" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="C63" s="32"/>
+      <c r="D63" s="32"/>
+      <c r="E63" s="32">
+        <v>2800</v>
+      </c>
+      <c r="F63" s="33"/>
+    </row>
+    <row r="64" spans="2:6">
+      <c r="B64" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C64" s="32"/>
+      <c r="D64" s="32"/>
+      <c r="E64" s="32">
+        <v>200</v>
+      </c>
+      <c r="F64" s="33"/>
+    </row>
+    <row r="65" spans="2:6">
+      <c r="B65" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" s="32"/>
+      <c r="D65" s="32"/>
+      <c r="E65" s="32">
+        <v>1400</v>
+      </c>
+      <c r="F65" s="33"/>
+    </row>
+    <row r="66" spans="2:6">
+      <c r="B66" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" s="32"/>
+      <c r="D66" s="32"/>
+      <c r="E66" s="32">
+        <v>400</v>
+      </c>
+      <c r="F66" s="33"/>
+    </row>
+    <row r="67" spans="2:6">
+      <c r="B67" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C67" s="32"/>
+      <c r="D67" s="32"/>
+      <c r="E67" s="32">
+        <v>70</v>
+      </c>
+      <c r="F67" s="33"/>
+    </row>
+    <row r="68" spans="2:6">
+      <c r="B68" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C68" s="32"/>
+      <c r="D68" s="32"/>
+      <c r="E68" s="32">
+        <v>1380</v>
+      </c>
+      <c r="F68" s="33"/>
+    </row>
+    <row r="69" spans="2:6">
+      <c r="B69" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="C69" s="32"/>
+      <c r="D69" s="32"/>
+      <c r="E69" s="32">
+        <v>3200</v>
+      </c>
+      <c r="F69" s="33"/>
+    </row>
+    <row r="70" spans="2:6">
+      <c r="B70" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="C70" s="32"/>
+      <c r="D70" s="32"/>
+      <c r="E70" s="32">
+        <v>190</v>
+      </c>
+      <c r="F70" s="33"/>
+    </row>
+    <row r="71" spans="2:6">
+      <c r="B71" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="C71" s="32"/>
+      <c r="D71" s="32"/>
+      <c r="E71" s="32">
+        <v>35</v>
+      </c>
+      <c r="F71" s="33"/>
+    </row>
+    <row r="72" spans="2:6">
+      <c r="B72" s="31" t="s">
+        <v>165</v>
+      </c>
+      <c r="C72" s="32">
+        <v>49000</v>
+      </c>
+      <c r="D72" s="32"/>
+      <c r="E72" s="32"/>
+      <c r="F72" s="33"/>
+    </row>
+    <row r="73" spans="2:6" ht="17.25" thickBot="1">
+      <c r="B73" s="34"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="35"/>
+      <c r="E73" s="35"/>
+      <c r="F73" s="33"/>
+    </row>
+    <row r="74" spans="2:6" ht="17.25" thickBot="1">
+      <c r="B74" s="36" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="37">
-        <f>SUM(C4:C32)*C3</f>
-        <v>1853692</v>
-      </c>
-      <c r="D33" s="37">
-        <f>SUM(D4:D32)*D3</f>
+      <c r="C74" s="37">
+        <f>SUM(C4:C73)*C3</f>
+        <v>1761492</v>
+      </c>
+      <c r="D74" s="37">
+        <f>SUM(D4:D73)*D3</f>
         <v>0</v>
       </c>
-      <c r="E33" s="37">
-        <f>SUM(E4:E32)*E3</f>
-        <v>143040</v>
-      </c>
-      <c r="F33" s="38">
-        <f>SUM(C33:E33)</f>
-        <v>1996732</v>
+      <c r="E74" s="37">
+        <f>SUM(E4:E73)*E3</f>
+        <v>1296470.456</v>
+      </c>
+      <c r="F74" s="38">
+        <f>SUM(C74:E74)</f>
+        <v>3057962.4560000002</v>
       </c>
     </row>
   </sheetData>
@@ -3020,42 +3889,42 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:21">
-      <c r="B3" s="51" t="s">
+      <c r="B3" s="47" t="s">
+        <v>93</v>
+      </c>
+      <c r="J3" s="47" t="s">
+        <v>90</v>
+      </c>
+      <c r="K3" s="47" t="s">
         <v>95</v>
       </c>
-      <c r="J3" s="51" t="s">
+      <c r="U3" s="47" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="28" spans="2:12">
+      <c r="B28" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="K28" s="47" t="s">
+        <v>91</v>
+      </c>
+      <c r="L28" s="47" t="s">
         <v>92</v>
       </c>
-      <c r="K3" s="51" t="s">
-        <v>97</v>
-      </c>
-      <c r="U3" s="51" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="2:12">
-      <c r="B28" s="51" t="s">
+    </row>
+    <row r="47" spans="2:15">
+      <c r="B47" s="47" t="s">
         <v>99</v>
       </c>
-      <c r="G28" s="51" t="s">
+      <c r="I47" s="47" t="s">
+        <v>100</v>
+      </c>
+      <c r="O47" s="47" t="s">
         <v>98</v>
-      </c>
-      <c r="K28" s="51" t="s">
-        <v>93</v>
-      </c>
-      <c r="L28" s="51" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="47" spans="2:15">
-      <c r="B47" s="51" t="s">
-        <v>101</v>
-      </c>
-      <c r="I47" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="O47" s="51" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
